--- a/docs/design/ACSMS-SCR-009/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_管理支店マスタ登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-009/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_管理支店マスタ登録画面_V1.0.xlsx
@@ -15,7 +15,7 @@
     <sheet name="ACSMS-API-009-001" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ACSMS-API-009-002" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ACSMS-API-009-003" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ACSMS-API-009-004" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ACSMS-API-COMMON-001" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1702,7 +1702,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1992,7 +1992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -2153,7 +2153,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2270,7 +2270,7 @@
       <c r="B6" s="11" t="n"/>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>UNAUTHORIZED</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -2281,7 +2281,7 @@
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>UNAUTHORIZED</t>
+          <t>BAD_REQUEST</t>
         </is>
       </c>
       <c r="K6" s="10" t="n"/>
@@ -2297,7 +2297,7 @@
       <c r="U6" s="11" t="n"/>
       <c r="V6" s="19" t="inlineStr">
         <is>
-          <t>セッションが切れました。再度ログインしてください。</t>
+          <t>リクエストパラメータが不正です。</t>
         </is>
       </c>
       <c r="W6" s="10" t="n"/>
@@ -2323,7 +2323,7 @@
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>FORBIDDEN</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D7" s="10" t="n"/>
@@ -2334,7 +2334,7 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>FORBIDDEN</t>
+          <t>UNAUTHORIZED</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
@@ -2350,7 +2350,7 @@
       <c r="U7" s="11" t="n"/>
       <c r="V7" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません。</t>
+          <t>セッションが切れました。再度ログインしてください。</t>
         </is>
       </c>
       <c r="W7" s="10" t="n"/>
@@ -2376,7 +2376,7 @@
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D8" s="10" t="n"/>
@@ -2387,7 +2387,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>FORBIDDEN</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -2403,7 +2403,7 @@
       <c r="U8" s="11" t="n"/>
       <c r="V8" s="19" t="inlineStr">
         <is>
-          <t>指定された管理支店が見つかりません。</t>
+          <t>この画面へのアクセス権限がありません。</t>
         </is>
       </c>
       <c r="W8" s="10" t="n"/>
@@ -2429,7 +2429,7 @@
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>BAD_REQUEST</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D9" s="10" t="n"/>
@@ -2440,7 +2440,7 @@
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>BAD_REQUEST</t>
+          <t>DATA_SCOPE_VIOLATION</t>
         </is>
       </c>
       <c r="K9" s="10" t="n"/>
@@ -2456,7 +2456,7 @@
       <c r="U9" s="11" t="n"/>
       <c r="V9" s="19" t="inlineStr">
         <is>
-          <t>リクエストパラメータが不正です。</t>
+          <t>このデータへのアクセス権限がありません。</t>
         </is>
       </c>
       <c r="W9" s="10" t="n"/>
@@ -2482,7 +2482,7 @@
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>VALIDATION_ERROR</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -2535,7 +2535,7 @@
       <c r="B11" s="11" t="n"/>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D11" s="10" t="n"/>
@@ -2546,7 +2546,7 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>TOO_MANY_REQUESTS</t>
         </is>
       </c>
       <c r="K11" s="10" t="n"/>
@@ -2562,7 +2562,7 @@
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="19" t="inlineStr">
         <is>
-          <t>この管理支店コードは既に登録されています。</t>
+          <t>リクエスト回数が上限を超えました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
       <c r="W11" s="10" t="n"/>
@@ -2588,7 +2588,7 @@
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>INTERNAL_SERVER_ERROR</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -2634,35 +2634,259 @@
       <c r="AJ12" s="10" t="n"/>
       <c r="AK12" s="11" t="n"/>
     </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="11" t="n"/>
+      <c r="V13" s="19" t="inlineStr">
+        <is>
+          <t>指定された管理支店が見つかりません。</t>
+        </is>
+      </c>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>DUPLICATE_CODE</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="11" t="n"/>
+      <c r="V14" s="19" t="inlineStr">
+        <is>
+          <t>管理支店コード「{kanri_shiten_code}」はすでに登録されています。</t>
+        </is>
+      </c>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
+      <c r="AB14" s="10" t="n"/>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="10" t="n"/>
+      <c r="AH14" s="10" t="n"/>
+      <c r="AI14" s="10" t="n"/>
+      <c r="AJ14" s="10" t="n"/>
+      <c r="AK14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>BAD_REQUEST</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="11" t="n"/>
+      <c r="V15" s="19" t="inlineStr">
+        <is>
+          <t>都道府県コードが存在しません。</t>
+        </is>
+      </c>
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="10" t="n"/>
+      <c r="Y15" s="10" t="n"/>
+      <c r="Z15" s="10" t="n"/>
+      <c r="AA15" s="10" t="n"/>
+      <c r="AB15" s="10" t="n"/>
+      <c r="AC15" s="10" t="n"/>
+      <c r="AD15" s="10" t="n"/>
+      <c r="AE15" s="10" t="n"/>
+      <c r="AF15" s="10" t="n"/>
+      <c r="AG15" s="10" t="n"/>
+      <c r="AH15" s="10" t="n"/>
+      <c r="AI15" s="10" t="n"/>
+      <c r="AJ15" s="10" t="n"/>
+      <c r="AK15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>BAD_REQUEST</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="11" t="n"/>
+      <c r="V16" s="19" t="inlineStr">
+        <is>
+          <t>JA IDが存在しません。</t>
+        </is>
+      </c>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="10" t="n"/>
+      <c r="AA16" s="10" t="n"/>
+      <c r="AB16" s="10" t="n"/>
+      <c r="AC16" s="10" t="n"/>
+      <c r="AD16" s="10" t="n"/>
+      <c r="AE16" s="10" t="n"/>
+      <c r="AF16" s="10" t="n"/>
+      <c r="AG16" s="10" t="n"/>
+      <c r="AH16" s="10" t="n"/>
+      <c r="AI16" s="10" t="n"/>
+      <c r="AJ16" s="10" t="n"/>
+      <c r="AK16" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="62">
     <mergeCell ref="V11:AK11"/>
+    <mergeCell ref="J15:U15"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="J6:U6"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="V16:AK16"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="V7:AK7"/>
     <mergeCell ref="J11:U11"/>
+    <mergeCell ref="C13:I13"/>
     <mergeCell ref="J7:U7"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="J16:U16"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="V12:AK12"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="C15:I15"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C14:I14"/>
     <mergeCell ref="J12:U12"/>
     <mergeCell ref="V5:AK5"/>
     <mergeCell ref="V8:AK8"/>
+    <mergeCell ref="V14:AK14"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="V13:AK13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C16:I16"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J8:U8"/>
     <mergeCell ref="A8:B8"/>
@@ -2673,14 +2897,18 @@
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="J5:U5"/>
     <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J14:U14"/>
     <mergeCell ref="J10:U10"/>
     <mergeCell ref="V9:AK9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C12:I12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="J13:U13"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="V6:AK6"/>
     <mergeCell ref="C11:I11"/>
+    <mergeCell ref="V15:AK15"/>
     <mergeCell ref="J9:U9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2854,7 +3082,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3146,7 +3374,7 @@
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>ACSMS-API-009-004</t>
+          <t>ACSMS-API-COMMON-001</t>
         </is>
       </c>
       <c r="D9" s="10" t="n"/>
@@ -3254,7 +3482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK90"/>
+  <dimension ref="A1:AK95"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3415,7 +3643,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4397,14 +4625,14 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="36" customHeight="1">
       <c r="B31" s="31" t="n">
         <v>4</v>
       </c>
       <c r="C31" s="38" t="n"/>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_code</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E31" s="10" t="n"/>
@@ -4448,7 +4676,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>管理支店コード</t>
+          <t>JA名（m_jaからJOIN。JA_KANRI_SHITENはja.view権限を持たないためこの値でJA名を表示する）</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -4464,7 +4692,7 @@
       <c r="C32" s="38" t="n"/>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>kanri_shiten_code</t>
         </is>
       </c>
       <c r="E32" s="10" t="n"/>
@@ -4508,7 +4736,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>管理支店名</t>
+          <t>管理支店コード</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -4524,7 +4752,7 @@
       <c r="C33" s="38" t="n"/>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name_kana</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E33" s="10" t="n"/>
@@ -4557,7 +4785,7 @@
       <c r="X33" s="11" t="n"/>
       <c r="Y33" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z33" s="10" t="n"/>
@@ -4568,7 +4796,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>管理支店名（カナ）</t>
+          <t>管理支店名</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -4584,7 +4812,7 @@
       <c r="C34" s="38" t="n"/>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>kanri_shiten_name_kana</t>
         </is>
       </c>
       <c r="E34" s="10" t="n"/>
@@ -4628,7 +4856,7 @@
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード</t>
+          <t>管理支店名（カナ）</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -4644,7 +4872,7 @@
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>todofuken_name</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E35" s="10" t="n"/>
@@ -4688,7 +4916,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>都道府県名（JOINで取得）</t>
+          <t>都道府県コード</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -4704,7 +4932,7 @@
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
@@ -4737,7 +4965,7 @@
       <c r="X36" s="11" t="n"/>
       <c r="Y36" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z36" s="10" t="n"/>
@@ -4748,7 +4976,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>都道府県名（JOINで取得）</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4764,7 +4992,7 @@
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -4797,7 +5025,7 @@
       <c r="X37" s="11" t="n"/>
       <c r="Y37" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z37" s="10" t="n"/>
@@ -4808,7 +5036,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4824,7 +5052,7 @@
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4857,7 +5085,7 @@
       <c r="X38" s="11" t="n"/>
       <c r="Y38" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z38" s="10" t="n"/>
@@ -4868,7 +5096,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4884,7 +5112,7 @@
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4917,7 +5145,7 @@
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z39" s="10" t="n"/>
@@ -4928,7 +5156,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -4944,7 +5172,7 @@
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -4957,7 +5185,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -4988,7 +5216,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -5004,7 +5232,7 @@
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5048,7 +5276,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ</t>
+          <t>紙版取扱フラグ</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5064,7 +5292,7 @@
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>denshi_flg</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -5077,7 +5305,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -5097,7 +5325,7 @@
       <c r="X42" s="11" t="n"/>
       <c r="Y42" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z42" s="10" t="n"/>
@@ -5108,7 +5336,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>電子版取扱フラグ</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5124,7 +5352,7 @@
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5150,11 +5378,7 @@
       </c>
       <c r="R43" s="10" t="n"/>
       <c r="S43" s="11" t="n"/>
-      <c r="T43" s="17" t="inlineStr">
-        <is>
-          <t>ISO 8601</t>
-        </is>
-      </c>
+      <c r="T43" s="17" t="inlineStr"/>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
       <c r="W43" s="10" t="n"/>
@@ -5172,7 +5396,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5185,10 +5409,10 @@
       <c r="B44" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="C44" s="39" t="n"/>
+      <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5225,7 +5449,7 @@
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z44" s="10" t="n"/>
@@ -5236,7 +5460,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5245,72 +5469,137 @@
       <c r="AJ44" s="10" t="n"/>
       <c r="AK44" s="11" t="n"/>
     </row>
-    <row r="45" ht="19.5" customHeight="1"/>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="B46" s="40" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n"/>
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="11" t="n"/>
+      <c r="T45" s="17" t="inlineStr">
+        <is>
+          <t>ISO 8601</t>
+        </is>
+      </c>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n"/>
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="11" t="n"/>
+      <c r="Y45" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z45" s="10" t="n"/>
+      <c r="AA45" s="10" t="n"/>
+      <c r="AB45" s="10" t="n"/>
+      <c r="AC45" s="10" t="n"/>
+      <c r="AD45" s="10" t="n"/>
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG45" s="10" t="n"/>
+      <c r="AH45" s="10" t="n"/>
+      <c r="AI45" s="10" t="n"/>
+      <c r="AJ45" s="10" t="n"/>
+      <c r="AK45" s="11" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1"/>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="C47" s="19" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/kanri-shiten/1</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="10" t="n"/>
-      <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n"/>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="10" t="n"/>
-      <c r="N47" s="10" t="n"/>
-      <c r="O47" s="10" t="n"/>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="10" t="n"/>
-      <c r="R47" s="10" t="n"/>
-      <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="n"/>
-      <c r="U47" s="10" t="n"/>
-      <c r="V47" s="10" t="n"/>
-      <c r="W47" s="10" t="n"/>
-      <c r="X47" s="10" t="n"/>
-      <c r="Y47" s="10" t="n"/>
-      <c r="Z47" s="10" t="n"/>
-      <c r="AA47" s="10" t="n"/>
-      <c r="AB47" s="10" t="n"/>
-      <c r="AC47" s="10" t="n"/>
-      <c r="AD47" s="10" t="n"/>
-      <c r="AE47" s="10" t="n"/>
-      <c r="AF47" s="10" t="n"/>
-      <c r="AG47" s="10" t="n"/>
-      <c r="AH47" s="10" t="n"/>
-      <c r="AI47" s="10" t="n"/>
-      <c r="AJ47" s="10" t="n"/>
-      <c r="AK47" s="11" t="n"/>
-    </row>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="B49" s="40" t="inlineStr">
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="10" t="n"/>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="10" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="10" t="n"/>
+      <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
+      <c r="AB48" s="10" t="n"/>
+      <c r="AC48" s="10" t="n"/>
+      <c r="AD48" s="10" t="n"/>
+      <c r="AE48" s="10" t="n"/>
+      <c r="AF48" s="10" t="n"/>
+      <c r="AG48" s="10" t="n"/>
+      <c r="AH48" s="10" t="n"/>
+      <c r="AI48" s="10" t="n"/>
+      <c r="AJ48" s="10" t="n"/>
+      <c r="AK48" s="11" t="n"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="360" customHeight="1">
-      <c r="C50" s="19" t="inlineStr">
+    <row r="51" ht="378" customHeight="1">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
     "kanri_shiten_id": 1,
     "ja_id": 1,
+    "ja_name": "JA東京",
     "kanri_shiten_code": "113-3300-001",
     "kanri_shiten_name": "東京中央会支店",
-    "kanri_shiten_name_kana": "トウキョウチュウオウカイシテン",
+    "kanri_shiten_name_kana": "ﾄｳｷｮｳﾁｭｳｵｳｶｲｼﾃﾝ",
     "todofuken_code": "13",
     "todofuken_name": "東京都",
     "yubin_no": "1000001",
@@ -5326,50 +5615,50 @@
 }</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
-      <c r="I50" s="10" t="n"/>
-      <c r="J50" s="10" t="n"/>
-      <c r="K50" s="10" t="n"/>
-      <c r="L50" s="10" t="n"/>
-      <c r="M50" s="10" t="n"/>
-      <c r="N50" s="10" t="n"/>
-      <c r="O50" s="10" t="n"/>
-      <c r="P50" s="10" t="n"/>
-      <c r="Q50" s="10" t="n"/>
-      <c r="R50" s="10" t="n"/>
-      <c r="S50" s="10" t="n"/>
-      <c r="T50" s="10" t="n"/>
-      <c r="U50" s="10" t="n"/>
-      <c r="V50" s="10" t="n"/>
-      <c r="W50" s="10" t="n"/>
-      <c r="X50" s="10" t="n"/>
-      <c r="Y50" s="10" t="n"/>
-      <c r="Z50" s="10" t="n"/>
-      <c r="AA50" s="10" t="n"/>
-      <c r="AB50" s="10" t="n"/>
-      <c r="AC50" s="10" t="n"/>
-      <c r="AD50" s="10" t="n"/>
-      <c r="AE50" s="10" t="n"/>
-      <c r="AF50" s="10" t="n"/>
-      <c r="AG50" s="10" t="n"/>
-      <c r="AH50" s="10" t="n"/>
-      <c r="AI50" s="10" t="n"/>
-      <c r="AJ50" s="10" t="n"/>
-      <c r="AK50" s="11" t="n"/>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="B52" s="40" t="inlineStr">
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="10" t="n"/>
+      <c r="AF51" s="10" t="n"/>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="72" customHeight="1">
-      <c r="C53" s="19" t="inlineStr">
+    <row r="54" ht="72" customHeight="1">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -5377,50 +5666,50 @@
 }</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="10" t="n"/>
-      <c r="M53" s="10" t="n"/>
-      <c r="N53" s="10" t="n"/>
-      <c r="O53" s="10" t="n"/>
-      <c r="P53" s="10" t="n"/>
-      <c r="Q53" s="10" t="n"/>
-      <c r="R53" s="10" t="n"/>
-      <c r="S53" s="10" t="n"/>
-      <c r="T53" s="10" t="n"/>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n"/>
-      <c r="X53" s="10" t="n"/>
-      <c r="Y53" s="10" t="n"/>
-      <c r="Z53" s="10" t="n"/>
-      <c r="AA53" s="10" t="n"/>
-      <c r="AB53" s="10" t="n"/>
-      <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="10" t="n"/>
-      <c r="AE53" s="10" t="n"/>
-      <c r="AF53" s="10" t="n"/>
-      <c r="AG53" s="10" t="n"/>
-      <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="10" t="n"/>
-      <c r="AJ53" s="10" t="n"/>
-      <c r="AK53" s="11" t="n"/>
-    </row>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="B55" s="40" t="inlineStr">
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="72" customHeight="1">
-      <c r="C56" s="19" t="inlineStr">
+    <row r="57" ht="72" customHeight="1">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -5428,50 +5717,50 @@
 }</t>
         </is>
       </c>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
-      <c r="J56" s="10" t="n"/>
-      <c r="K56" s="10" t="n"/>
-      <c r="L56" s="10" t="n"/>
-      <c r="M56" s="10" t="n"/>
-      <c r="N56" s="10" t="n"/>
-      <c r="O56" s="10" t="n"/>
-      <c r="P56" s="10" t="n"/>
-      <c r="Q56" s="10" t="n"/>
-      <c r="R56" s="10" t="n"/>
-      <c r="S56" s="10" t="n"/>
-      <c r="T56" s="10" t="n"/>
-      <c r="U56" s="10" t="n"/>
-      <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n"/>
-      <c r="X56" s="10" t="n"/>
-      <c r="Y56" s="10" t="n"/>
-      <c r="Z56" s="10" t="n"/>
-      <c r="AA56" s="10" t="n"/>
-      <c r="AB56" s="10" t="n"/>
-      <c r="AC56" s="10" t="n"/>
-      <c r="AD56" s="10" t="n"/>
-      <c r="AE56" s="10" t="n"/>
-      <c r="AF56" s="10" t="n"/>
-      <c r="AG56" s="10" t="n"/>
-      <c r="AH56" s="10" t="n"/>
-      <c r="AI56" s="10" t="n"/>
-      <c r="AJ56" s="10" t="n"/>
-      <c r="AK56" s="11" t="n"/>
-    </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="B58" s="40" t="inlineStr">
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="72" customHeight="1">
-      <c r="C59" s="19" t="inlineStr">
+    <row r="60" ht="72" customHeight="1">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -5479,50 +5768,50 @@
 }</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n"/>
-      <c r="E59" s="10" t="n"/>
-      <c r="F59" s="10" t="n"/>
-      <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="10" t="n"/>
-      <c r="M59" s="10" t="n"/>
-      <c r="N59" s="10" t="n"/>
-      <c r="O59" s="10" t="n"/>
-      <c r="P59" s="10" t="n"/>
-      <c r="Q59" s="10" t="n"/>
-      <c r="R59" s="10" t="n"/>
-      <c r="S59" s="10" t="n"/>
-      <c r="T59" s="10" t="n"/>
-      <c r="U59" s="10" t="n"/>
-      <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n"/>
-      <c r="X59" s="10" t="n"/>
-      <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="10" t="n"/>
-      <c r="AA59" s="10" t="n"/>
-      <c r="AB59" s="10" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="10" t="n"/>
-      <c r="AF59" s="10" t="n"/>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="10" t="n"/>
-      <c r="AK59" s="11" t="n"/>
-    </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="B61" s="40" t="inlineStr">
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="72" customHeight="1">
-      <c r="C62" s="19" t="inlineStr">
+    <row r="63" ht="72" customHeight="1">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -5530,184 +5819,212 @@
 }</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n"/>
-      <c r="E62" s="10" t="n"/>
-      <c r="F62" s="10" t="n"/>
-      <c r="G62" s="10" t="n"/>
-      <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="n"/>
-      <c r="J62" s="10" t="n"/>
-      <c r="K62" s="10" t="n"/>
-      <c r="L62" s="10" t="n"/>
-      <c r="M62" s="10" t="n"/>
-      <c r="N62" s="10" t="n"/>
-      <c r="O62" s="10" t="n"/>
-      <c r="P62" s="10" t="n"/>
-      <c r="Q62" s="10" t="n"/>
-      <c r="R62" s="10" t="n"/>
-      <c r="S62" s="10" t="n"/>
-      <c r="T62" s="10" t="n"/>
-      <c r="U62" s="10" t="n"/>
-      <c r="V62" s="10" t="n"/>
-      <c r="W62" s="10" t="n"/>
-      <c r="X62" s="10" t="n"/>
-      <c r="Y62" s="10" t="n"/>
-      <c r="Z62" s="10" t="n"/>
-      <c r="AA62" s="10" t="n"/>
-      <c r="AB62" s="10" t="n"/>
-      <c r="AC62" s="10" t="n"/>
-      <c r="AD62" s="10" t="n"/>
-      <c r="AE62" s="10" t="n"/>
-      <c r="AF62" s="10" t="n"/>
-      <c r="AG62" s="10" t="n"/>
-      <c r="AH62" s="10" t="n"/>
-      <c r="AI62" s="10" t="n"/>
-      <c r="AJ62" s="10" t="n"/>
-      <c r="AK62" s="11" t="n"/>
-    </row>
-    <row r="64" ht="19.5" customHeight="1"/>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="27" t="inlineStr">
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1"/>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="27" t="inlineStr">
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
+    <row r="68" ht="18" customHeight="1">
+      <c r="C68" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="D68" s="41" t="inlineStr">
-        <is>
-          <t>`kanri_shiten_id`：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="D69" s="41" t="inlineStr">
         <is>
+          <t>`kanri_shiten_id`：数値型チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="D70" s="41" t="inlineStr">
+        <is>
           <t>`kanri_shiten_id`：必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="D71" s="41" t="inlineStr">
+    <row r="72" ht="18" customHeight="1">
+      <c r="D72" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="C74" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="C75" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`kanri-shiten.view` を保持しているか確認する。</t>
+          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden</t>
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`kanri_shiten.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="D77" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN / CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden（ACSMS-MSG-009-006）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>基本条件：</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
+    <row r="81" ht="36" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
         <is>
           <t>`m_kanri_shiten.kanri_shiten_id` = `:kanri_shiten_id`</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="D82" s="41" t="inlineStr">
         <is>
           <t>`m_kanri_shiten.deleted_at IS NULL`</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>NICHINO_ADMIN はデータスコープ制限なし（全JA管理支店にアクセス可能）。</t>
-        </is>
-      </c>
-    </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="27" t="inlineStr">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>データスコープ（画面定義§1.3）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="D84" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_ADMIN：制限なし（全JA管理支店にアクセス可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="D85" s="41" t="inlineStr">
+        <is>
+          <t>CHUOKAI / JA_HONTEN：自JAの管理支店のみ（`mks.ja_id = session.ja_id`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="54" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>JA_KANRI_SHITEN：自JA自管理支店のみ（`mks.ja_id = session.ja_id AND mks.kanri_shiten_id = session.kanri_shiten_id`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>スコープ違反の場合：HTTP 404 Not Found（ACSMS-MSG-009-005）を返す（行の存在を漏らさない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>4.4 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
+    <row r="89" ht="18" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行してデータを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="378" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
+    <row r="90" ht="378" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>SELECT
     mks.kanri_shiten_id,
@@ -5732,115 +6049,117 @@
   AND mks.deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="C91" s="41" t="inlineStr">
         <is>
           <t>対象レコードが存在しない場合：HTTP 404 Not Found を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>4.5 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
         <is>
           <t>取得した管理支店データを JSON 形式で返却する。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="B89" s="27" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>4.6 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
+    <row r="95" ht="18" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 Internal Server Error を返却する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="203">
+  <mergeCells count="213">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C53:AK53"/>
-    <mergeCell ref="D71:AK71"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
-    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="D35:L35"/>
     <mergeCell ref="Q43:S43"/>
@@ -5849,36 +6168,40 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="C51:AK51"/>
+    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="D34:L34"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="A65:AK65"/>
+    <mergeCell ref="D77:AK77"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="C48:AK48"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="D36:L36"/>
-    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="M33:P33"/>
+    <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="D72:AK72"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="T38:X38"/>
-    <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="B67:AK67"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="D37:L37"/>
+    <mergeCell ref="C29:C45"/>
     <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="D39:L39"/>
@@ -5887,6 +6210,7 @@
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D29:L29"/>
     <mergeCell ref="Q32:S32"/>
@@ -5897,17 +6221,16 @@
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="B89:AK89"/>
-    <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
-    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="A25:AK25"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="D76:AK76"/>
+    <mergeCell ref="A66:AK66"/>
+    <mergeCell ref="B50:I50"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="M37:P37"/>
@@ -5916,94 +6239,98 @@
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C62:AK62"/>
+    <mergeCell ref="AF45:AK45"/>
     <mergeCell ref="Y41:AE41"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="B61:I61"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C54:AK54"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C50:AK50"/>
+    <mergeCell ref="C93:AK93"/>
+    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="Y44:AE44"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
-    <mergeCell ref="B55:I55"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="B72:AK72"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="M38:P38"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B52:I52"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D68:AK68"/>
+    <mergeCell ref="B88:AK88"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="D85:AK85"/>
+    <mergeCell ref="B53:I53"/>
     <mergeCell ref="D69:AK69"/>
-    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
-    <mergeCell ref="C29:C44"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="D31:L31"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="D70:AK70"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
@@ -6018,7 +6345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK124"/>
+  <dimension ref="A1:AK129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6179,7 +6506,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6582,7 +6909,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常に管理支店を登録しました</t>
+          <t>登録しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -6620,7 +6947,7 @@
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>入力内容にエラーがあります</t>
+          <t>入力内容にエラーがあります／管理支店コードが既に登録されています</t>
         </is>
       </c>
       <c r="O15" s="10" t="n"/>
@@ -6724,17 +7051,23 @@
       <c r="AK17" s="11" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="35" t="n"/>
-      <c r="I18" s="36" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="26" t="n"/>
       <c r="J18" s="17" t="n">
-        <v>409</v>
+        <v>500</v>
       </c>
       <c r="K18" s="10" t="n"/>
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>この管理支店コードは既に登録されています</t>
+          <t>システムエラーが発生しました</t>
         </is>
       </c>
       <c r="O18" s="10" t="n"/>
@@ -6761,68 +7094,92 @@
       <c r="AJ18" s="10" t="n"/>
       <c r="AK18" s="11" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="19" t="inlineStr">
-        <is>
-          <t>システムエラーが発生しました</t>
-        </is>
-      </c>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="10" t="n"/>
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="n"/>
-      <c r="AA19" s="10" t="n"/>
-      <c r="AB19" s="10" t="n"/>
-      <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="10" t="n"/>
-      <c r="AE19" s="10" t="n"/>
-      <c r="AF19" s="10" t="n"/>
-      <c r="AG19" s="10" t="n"/>
-      <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="10" t="n"/>
-      <c r="AJ19" s="10" t="n"/>
-      <c r="AK19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1"/>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+    <row r="19" ht="19.5" customHeight="1"/>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>2. リクエストパラメータ</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1"/>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="B23" s="30" t="inlineStr">
+    <row r="21" ht="19.5" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>パラメーターID</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="11" t="n"/>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="11" t="n"/>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="11" t="n"/>
+      <c r="Y22" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
+      </c>
+      <c r="Z22" s="10" t="n"/>
+      <c r="AA22" s="10" t="n"/>
+      <c r="AB22" s="11" t="n"/>
+      <c r="AC22" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
+      </c>
+      <c r="AD22" s="10" t="n"/>
+      <c r="AE22" s="11" t="n"/>
+      <c r="AF22" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG22" s="10" t="n"/>
+      <c r="AH22" s="10" t="n"/>
+      <c r="AI22" s="10" t="n"/>
+      <c r="AJ22" s="10" t="n"/>
+      <c r="AK22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="D23" s="10" t="n"/>
@@ -6834,48 +7191,40 @@
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="11" t="n"/>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
         </is>
       </c>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
       <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R23" s="10" t="n"/>
       <c r="S23" s="11" t="n"/>
-      <c r="T23" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="T23" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
         </is>
       </c>
       <c r="U23" s="10" t="n"/>
       <c r="V23" s="10" t="n"/>
       <c r="W23" s="10" t="n"/>
       <c r="X23" s="11" t="n"/>
-      <c r="Y23" s="16" t="inlineStr">
-        <is>
-          <t>最小長</t>
-        </is>
-      </c>
+      <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="10" t="n"/>
       <c r="AA23" s="10" t="n"/>
       <c r="AB23" s="11" t="n"/>
-      <c r="AC23" s="16" t="inlineStr">
-        <is>
-          <t>最大長</t>
-        </is>
-      </c>
+      <c r="AC23" s="17" t="inlineStr"/>
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="11" t="n"/>
-      <c r="AF23" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF23" s="19" t="inlineStr">
+        <is>
+          <t>JA ID（m_ja.ja_idに存在すること）</t>
         </is>
       </c>
       <c r="AG23" s="10" t="n"/>
@@ -6884,13 +7233,13 @@
       <c r="AJ23" s="10" t="n"/>
       <c r="AK23" s="11" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="54" customHeight="1">
       <c r="B24" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>kanri_shiten_code</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -6904,7 +7253,7 @@
       <c r="L24" s="11" t="n"/>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N24" s="10" t="n"/>
@@ -6930,12 +7279,14 @@
       <c r="Z24" s="10" t="n"/>
       <c r="AA24" s="10" t="n"/>
       <c r="AB24" s="11" t="n"/>
-      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AC24" s="17" t="n">
+        <v>12</v>
+      </c>
       <c r="AD24" s="10" t="n"/>
       <c r="AE24" s="11" t="n"/>
       <c r="AF24" s="19" t="inlineStr">
         <is>
-          <t>JA ID（m_ja.ja_idに存在すること）</t>
+          <t>管理支店コード（一意制約、論理削除後も再利用不可）。フォーマットは「NNN-NNNN-NNN」（半角数字とハイフンのみ）。ハイフン無しの10桁数字を入力した場合は自動的にハイフンを挿入して正規化する</t>
         </is>
       </c>
       <c r="AG24" s="10" t="n"/>
@@ -6946,11 +7297,11 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_code</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -6991,13 +7342,13 @@
       <c r="AA25" s="10" t="n"/>
       <c r="AB25" s="11" t="n"/>
       <c r="AC25" s="17" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AD25" s="10" t="n"/>
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>管理支店コード（一意制約）</t>
+          <t>管理支店名</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -7008,11 +7359,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>kanri_shiten_name_kana</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -7041,7 +7392,7 @@
       <c r="S26" s="11" t="n"/>
       <c r="T26" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U26" s="10" t="n"/>
@@ -7059,7 +7410,7 @@
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>管理支店名</t>
+          <t>管理支店名（カナ）。半角カタカナ・半角数字のみ（全角カタカナ・ひらがな不可）</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -7070,11 +7421,11 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name_kana</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -7103,25 +7454,27 @@
       <c r="S27" s="11" t="n"/>
       <c r="T27" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="17" t="inlineStr"/>
+      <c r="Y27" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="11" t="n"/>
       <c r="AC27" s="17" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>管理支店名（カナ）</t>
+          <t>都道府県コード（m_todofukenに存在すること）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -7132,11 +7485,11 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -7165,7 +7518,7 @@
       <c r="S28" s="11" t="n"/>
       <c r="T28" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U28" s="10" t="n"/>
@@ -7173,19 +7526,19 @@
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n"/>
       <c r="Y28" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
       <c r="AB28" s="11" t="n"/>
       <c r="AC28" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード（m_todofukenに存在すること）</t>
+          <t>郵便番号（半角数字7桁）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -7196,11 +7549,11 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>address</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -7236,20 +7589,18 @@
       <c r="V29" s="10" t="n"/>
       <c r="W29" s="10" t="n"/>
       <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="17" t="n">
-        <v>7</v>
-      </c>
+      <c r="Y29" s="17" t="inlineStr"/>
       <c r="Z29" s="10" t="n"/>
       <c r="AA29" s="10" t="n"/>
       <c r="AB29" s="11" t="n"/>
       <c r="AC29" s="17" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="AD29" s="10" t="n"/>
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>郵便番号（半角数字7桁）</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -7260,11 +7611,11 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -7305,13 +7656,13 @@
       <c r="AA30" s="10" t="n"/>
       <c r="AB30" s="11" t="n"/>
       <c r="AC30" s="17" t="n">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>電話番号（半角数字のみ）</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -7322,11 +7673,11 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -7373,7 +7724,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>電話番号（半角数字のみ）</t>
+          <t>FAX番号（半角数字のみ）</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -7384,11 +7735,11 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -7402,7 +7753,7 @@
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
@@ -7428,14 +7779,12 @@
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
       <c r="AB32" s="11" t="n"/>
-      <c r="AC32" s="17" t="n">
-        <v>15</v>
-      </c>
+      <c r="AC32" s="17" t="inlineStr"/>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>FAX番号（半角数字のみ）</t>
+          <t>紙版取扱フラグ（デフォルト: false）</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -7446,11 +7795,11 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>denshi_flg</t>
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
@@ -7495,7 +7844,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ（デフォルト: false）</t>
+          <t>電子版取扱フラグ（デフォルト: false）</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -7506,11 +7855,11 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -7524,7 +7873,7 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
@@ -7550,12 +7899,14 @@
       <c r="Z34" s="10" t="n"/>
       <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="11" t="n"/>
-      <c r="AC34" s="17" t="inlineStr"/>
+      <c r="AC34" s="17" t="n">
+        <v>500</v>
+      </c>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ（デフォルト: false）</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -7564,86 +7915,88 @@
       <c r="AJ34" s="10" t="n"/>
       <c r="AK34" s="11" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>biko</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="17" t="inlineStr"/>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="11" t="n"/>
-      <c r="AC35" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="19" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="10" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1"/>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="19.5" customHeight="1"/>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="B39" s="30" t="inlineStr">
+    <row r="37" ht="19.5" customHeight="1"/>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="11" t="n"/>
+      <c r="Y38" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
         </is>
       </c>
       <c r="D39" s="10" t="n"/>
@@ -7655,33 +8008,29 @@
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="11" t="n"/>
-      <c r="M39" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
       <c r="P39" s="11" t="n"/>
-      <c r="Q39" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R39" s="10" t="n"/>
       <c r="S39" s="11" t="n"/>
-      <c r="T39" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
+      <c r="T39" s="17" t="inlineStr"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="11" t="n"/>
-      <c r="Y39" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
+      <c r="Y39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="Z39" s="10" t="n"/>
@@ -7690,11 +8039,7 @@
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
       <c r="AE39" s="11" t="n"/>
-      <c r="AF39" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+      <c r="AF39" s="19" t="inlineStr"/>
       <c r="AG39" s="10" t="n"/>
       <c r="AH39" s="10" t="n"/>
       <c r="AI39" s="10" t="n"/>
@@ -7703,14 +8048,14 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>kanri_shiten_id</t>
+        </is>
+      </c>
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="10" t="n"/>
@@ -7721,7 +8066,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -7750,7 +8095,11 @@
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
       <c r="AE40" s="11" t="n"/>
-      <c r="AF40" s="19" t="inlineStr"/>
+      <c r="AF40" s="19" t="inlineStr">
+        <is>
+          <t>自動採番された管理支店ID</t>
+        </is>
+      </c>
       <c r="AG40" s="10" t="n"/>
       <c r="AH40" s="10" t="n"/>
       <c r="AI40" s="10" t="n"/>
@@ -7759,12 +8108,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" s="37" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -7808,7 +8157,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>自動採番された管理支店ID</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -7819,12 +8168,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -7837,7 +8186,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -7868,7 +8217,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>JA名（m_jaからJOIN）</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -7879,7 +8228,7 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
@@ -7939,7 +8288,7 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
@@ -7999,7 +8348,7 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
@@ -8037,7 +8386,7 @@
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z45" s="10" t="n"/>
@@ -8059,7 +8408,7 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
@@ -8119,12 +8468,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -8157,7 +8506,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -8168,7 +8517,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>都道府県名（m_todofukenからJOIN）</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -8179,12 +8528,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -8217,7 +8566,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -8228,7 +8577,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -8239,12 +8588,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -8277,7 +8626,7 @@
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z49" s="10" t="n"/>
@@ -8288,7 +8637,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -8299,12 +8648,12 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -8337,7 +8686,7 @@
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z50" s="10" t="n"/>
@@ -8348,7 +8697,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -8359,12 +8708,12 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -8377,7 +8726,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -8408,7 +8757,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -8419,12 +8768,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -8468,7 +8817,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ</t>
+          <t>紙版取扱フラグ</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -8479,12 +8828,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>denshi_flg</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -8497,7 +8846,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -8517,7 +8866,7 @@
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z53" s="10" t="n"/>
@@ -8528,7 +8877,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>電子版取扱フラグ</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -8539,12 +8888,12 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="C54" s="39" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -8570,11 +8919,7 @@
       </c>
       <c r="R54" s="10" t="n"/>
       <c r="S54" s="11" t="n"/>
-      <c r="T54" s="17" t="inlineStr">
-        <is>
-          <t>ISO 8601</t>
-        </is>
-      </c>
+      <c r="T54" s="17" t="inlineStr"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
       <c r="W54" s="10" t="n"/>
@@ -8592,7 +8937,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -8603,14 +8948,14 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
@@ -8634,7 +8979,11 @@
       </c>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr"/>
+      <c r="T55" s="17" t="inlineStr">
+        <is>
+          <t>ISO 8601</t>
+        </is>
+      </c>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
@@ -8652,7 +9001,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>処理結果メッセージ</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -8661,16 +9010,140 @@
       <c r="AJ55" s="10" t="n"/>
       <c r="AK55" s="11" t="n"/>
     </row>
-    <row r="56" ht="19.5" customHeight="1"/>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="B57" s="40" t="inlineStr">
+    <row r="56" ht="54" customHeight="1">
+      <c r="B56" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C56" s="39" t="n"/>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="11" t="n"/>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="11" t="n"/>
+      <c r="T56" s="17" t="inlineStr">
+        <is>
+          <t>ISO 8601</t>
+        </is>
+      </c>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="11" t="n"/>
+      <c r="Y56" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="10" t="n"/>
+      <c r="AE56" s="11" t="n"/>
+      <c r="AF56" s="19" t="inlineStr">
+        <is>
+          <t>更新日時（TypeORM `@UpdateDateColumn` は INSERT 時にも設定されるため created_at と同時刻の値が返る）</t>
+        </is>
+      </c>
+      <c r="AG56" s="10" t="n"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="10" t="n"/>
+      <c r="AJ56" s="10" t="n"/>
+      <c r="AK56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="11" t="n"/>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="17" t="inlineStr"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="11" t="n"/>
+      <c r="Y57" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="11" t="n"/>
+      <c r="AF57" s="19" t="inlineStr">
+        <is>
+          <t>処理結果メッセージ</t>
+        </is>
+      </c>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1"/>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="306" customHeight="1">
-      <c r="C58" s="19" t="inlineStr">
+    <row r="60" ht="306" customHeight="1">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/kanri-shiten
 Content-Type: application/json
@@ -8678,7 +9151,7 @@
   "ja_id": 1,
   "kanri_shiten_code": "113-3300-002",
   "kanri_shiten_name": "東京第二支店",
-  "kanri_shiten_name_kana": "トウキョウダイニシテン",
+  "kanri_shiten_name_kana": "ﾄｳｷｮｳﾀﾞｲﾆｼﾃﾝ",
   "todofuken_code": "13",
   "yubin_no": "1000002",
   "address": "千代田区千代田2-2-2",
@@ -8690,59 +9163,61 @@
 }</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="342" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
+    <row r="63" ht="396" customHeight="1">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
     "kanri_shiten_id": 2,
     "ja_id": 1,
+    "ja_name": "JA東京",
     "kanri_shiten_code": "113-3300-002",
     "kanri_shiten_name": "東京第二支店",
-    "kanri_shiten_name_kana": "トウキョウダイニシテン",
+    "kanri_shiten_name_kana": "ﾄｳｷｮｳﾀﾞｲﾆｼﾃﾝ",
     "todofuken_code": "13",
+    "todofuken_name": "東京都",
     "yubin_no": "1000002",
     "address": "千代田区千代田2-2-2",
     "tel": "0312345680",
@@ -8750,56 +9225,57 @@
     "paper_flg": true,
     "denshi_flg": true,
     "biko": "新規登録テスト",
-    "created_at": "2026-04-07T10:00:00Z"
+    "created_at": "2026-04-07T10:00:00Z",
+    "updated_at": "2026-04-07T10:00:00Z"
   },
-  "message": "管理支店を登録しました"
+  "message": "登録しました。"
 }</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="144" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="66" ht="144" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -8811,50 +9287,50 @@
 }</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="72" customHeight="1">
-      <c r="C67" s="19" t="inlineStr">
+    <row r="69" ht="72" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -8862,50 +9338,50 @@
 }</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="B69" s="40" t="inlineStr">
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="19" t="inlineStr">
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -8913,101 +9389,101 @@
 }</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="B72" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 409 Conflict）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="72" customHeight="1">
-      <c r="C73" s="19" t="inlineStr">
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="B74" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Duplicate Code）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="72" customHeight="1">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "CONFLICT",
-  "message": "この管理支店コードは既に登録されています"
+  "error_code": "DUPLICATE_CODE",
+  "message": "管理支店コード「113-3300-002」はすでに登録されています。"
 }</t>
         </is>
       </c>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="10" t="n"/>
-      <c r="M73" s="10" t="n"/>
-      <c r="N73" s="10" t="n"/>
-      <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="10" t="n"/>
-      <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
-      <c r="T73" s="10" t="n"/>
-      <c r="U73" s="10" t="n"/>
-      <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n"/>
-      <c r="X73" s="10" t="n"/>
-      <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
-      <c r="AA73" s="10" t="n"/>
-      <c r="AB73" s="10" t="n"/>
-      <c r="AC73" s="10" t="n"/>
-      <c r="AD73" s="10" t="n"/>
-      <c r="AE73" s="10" t="n"/>
-      <c r="AF73" s="10" t="n"/>
-      <c r="AG73" s="10" t="n"/>
-      <c r="AH73" s="10" t="n"/>
-      <c r="AI73" s="10" t="n"/>
-      <c r="AJ73" s="10" t="n"/>
-      <c r="AK73" s="11" t="n"/>
-    </row>
-    <row r="75" ht="19.5" customHeight="1">
-      <c r="B75" s="40" t="inlineStr">
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="B77" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="72" customHeight="1">
-      <c r="C76" s="19" t="inlineStr">
+    <row r="78" ht="72" customHeight="1">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -9015,283 +9491,320 @@
 }</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n"/>
-      <c r="E76" s="10" t="n"/>
-      <c r="F76" s="10" t="n"/>
-      <c r="G76" s="10" t="n"/>
-      <c r="H76" s="10" t="n"/>
-      <c r="I76" s="10" t="n"/>
-      <c r="J76" s="10" t="n"/>
-      <c r="K76" s="10" t="n"/>
-      <c r="L76" s="10" t="n"/>
-      <c r="M76" s="10" t="n"/>
-      <c r="N76" s="10" t="n"/>
-      <c r="O76" s="10" t="n"/>
-      <c r="P76" s="10" t="n"/>
-      <c r="Q76" s="10" t="n"/>
-      <c r="R76" s="10" t="n"/>
-      <c r="S76" s="10" t="n"/>
-      <c r="T76" s="10" t="n"/>
-      <c r="U76" s="10" t="n"/>
-      <c r="V76" s="10" t="n"/>
-      <c r="W76" s="10" t="n"/>
-      <c r="X76" s="10" t="n"/>
-      <c r="Y76" s="10" t="n"/>
-      <c r="Z76" s="10" t="n"/>
-      <c r="AA76" s="10" t="n"/>
-      <c r="AB76" s="10" t="n"/>
-      <c r="AC76" s="10" t="n"/>
-      <c r="AD76" s="10" t="n"/>
-      <c r="AE76" s="10" t="n"/>
-      <c r="AF76" s="10" t="n"/>
-      <c r="AG76" s="10" t="n"/>
-      <c r="AH76" s="10" t="n"/>
-      <c r="AI76" s="10" t="n"/>
-      <c r="AJ76" s="10" t="n"/>
-      <c r="AK76" s="11" t="n"/>
-    </row>
-    <row r="78" ht="19.5" customHeight="1"/>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="27" t="inlineStr">
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
+      <c r="AF78" s="10" t="n"/>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1"/>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="27" t="inlineStr">
+    <row r="82" ht="54" customHeight="1">
+      <c r="B82" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="10" t="n"/>
+      <c r="J82" s="10" t="n"/>
+      <c r="K82" s="10" t="n"/>
+      <c r="L82" s="10" t="n"/>
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="10" t="n"/>
+      <c r="R82" s="10" t="n"/>
+      <c r="S82" s="10" t="n"/>
+      <c r="T82" s="10" t="n"/>
+      <c r="U82" s="10" t="n"/>
+      <c r="V82" s="10" t="n"/>
+      <c r="W82" s="10" t="n"/>
+      <c r="X82" s="10" t="n"/>
+      <c r="Y82" s="10" t="n"/>
+      <c r="Z82" s="10" t="n"/>
+      <c r="AA82" s="10" t="n"/>
+      <c r="AB82" s="10" t="n"/>
+      <c r="AC82" s="10" t="n"/>
+      <c r="AD82" s="10" t="n"/>
+      <c r="AE82" s="10" t="n"/>
+      <c r="AF82" s="10" t="n"/>
+      <c r="AG82" s="10" t="n"/>
+      <c r="AH82" s="10" t="n"/>
+      <c r="AI82" s="10" t="n"/>
+      <c r="AJ82" s="10" t="n"/>
+      <c r="AK82" s="11" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="B83" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>リクエストボディの全フィールドを検証する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
-        <is>
-          <t>`ja_id`：必須、数値型</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>`kanri_shiten_code`：必須、最大15文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>`kanri_shiten_name`：必須、最大100文字</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>`kanri_shiten_name_kana`：任意、最大200文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
+          <t>`ja_id`：必須、数値型</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>`todofuken_code`：必須、2文字</t>
+          <t>`kanri_shiten_code`：必須、フォーマット「NNN-NNNN-NNN」（半角数字とハイフンのみ、12文字）。ハイフン無し10桁数字は自動的にハイフンを挿入して正規化する</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>`yubin_no`：任意、半角数字7桁</t>
+          <t>`kanri_shiten_name`：必須、最大100文字</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>`address`：任意、最大200文字</t>
+          <t>`kanri_shiten_name_kana`：任意、最大100文字、半角カタカナ・半角数字のみ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>`tel`：任意、半角数字のみ、最大15文字</t>
+          <t>`todofuken_code`：必須、2文字</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>`fax`：任意、半角数字のみ、最大15文字</t>
+          <t>`yubin_no`：任意、半角数字7桁</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="D91" s="41" t="inlineStr">
         <is>
-          <t>`paper_flg`：任意、ブール値（デフォルト: false）</t>
+          <t>`address`：任意、最大200文字</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="D92" s="41" t="inlineStr">
         <is>
-          <t>`denshi_flg`：任意、ブール値（デフォルト: false）</t>
+          <t>`tel`：任意、半角数字のみ、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="D93" s="41" t="inlineStr">
         <is>
-          <t>`biko`：任意、最大500文字</t>
+          <t>`fax`：任意、半角数字のみ、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="D94" s="41" t="inlineStr">
+        <is>
+          <t>`paper_flg`：任意、ブール値（デフォルト: false）</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="D95" s="41" t="inlineStr">
         <is>
+          <t>`denshi_flg`：任意、ブール値（デフォルト: false）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="D97" s="41" t="inlineStr">
+        <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="B96" s="27" t="inlineStr">
+    <row r="98" ht="18" customHeight="1">
+      <c r="B98" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`kanri-shiten.create`を保持しているか確認する。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="D100" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="C101" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden</t>
+          <t>権限チェック：`kanri_shiten.create`を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="B102" s="27" t="inlineStr">
-        <is>
-          <t>4.3 都道府県コードの存在検証</t>
+      <c r="D102" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="C103" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 Forbidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>4.3 都道府県コードの存在検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
+        <is>
           <t>`todofuken_code` が `m_todofuken` テーブルに存在することを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="54" customHeight="1">
-      <c r="C104" s="42" t="inlineStr">
+    <row r="106" ht="54" customHeight="1">
+      <c r="C106" s="42" t="inlineStr">
         <is>
           <t>SELECT todofuken_code
 FROM m_todofuken
 WHERE todofuken_code = :todofuken_code</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="10" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
-      <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
-      <c r="J104" s="10" t="n"/>
-      <c r="K104" s="10" t="n"/>
-      <c r="L104" s="10" t="n"/>
-      <c r="M104" s="10" t="n"/>
-      <c r="N104" s="10" t="n"/>
-      <c r="O104" s="10" t="n"/>
-      <c r="P104" s="10" t="n"/>
-      <c r="Q104" s="10" t="n"/>
-      <c r="R104" s="10" t="n"/>
-      <c r="S104" s="10" t="n"/>
-      <c r="T104" s="10" t="n"/>
-      <c r="U104" s="10" t="n"/>
-      <c r="V104" s="10" t="n"/>
-      <c r="W104" s="10" t="n"/>
-      <c r="X104" s="10" t="n"/>
-      <c r="Y104" s="10" t="n"/>
-      <c r="Z104" s="10" t="n"/>
-      <c r="AA104" s="10" t="n"/>
-      <c r="AB104" s="10" t="n"/>
-      <c r="AC104" s="10" t="n"/>
-      <c r="AD104" s="10" t="n"/>
-      <c r="AE104" s="10" t="n"/>
-      <c r="AF104" s="10" t="n"/>
-      <c r="AG104" s="10" t="n"/>
-      <c r="AH104" s="10" t="n"/>
-      <c r="AI104" s="10" t="n"/>
-      <c r="AJ104" s="10" t="n"/>
-      <c r="AK104" s="11" t="n"/>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
-        <is>
-          <t>存在しない場合：HTTP 400 Bad Request を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="B106" s="27" t="inlineStr">
-        <is>
-          <t>4.4 JA IDの存在検証</t>
-        </is>
-      </c>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="10" t="n"/>
+      <c r="K106" s="10" t="n"/>
+      <c r="L106" s="10" t="n"/>
+      <c r="M106" s="10" t="n"/>
+      <c r="N106" s="10" t="n"/>
+      <c r="O106" s="10" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="10" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="n"/>
+      <c r="V106" s="10" t="n"/>
+      <c r="W106" s="10" t="n"/>
+      <c r="X106" s="10" t="n"/>
+      <c r="Y106" s="10" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="10" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="10" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="10" t="n"/>
+      <c r="AK106" s="11" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="C107" s="41" t="inlineStr">
         <is>
+          <t>存在しない場合：HTTP 400 Bad Request を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>4.4 JA IDの存在検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
+        <is>
           <t>`ja_id` が `m_ja` テーブルに存在することを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="72" customHeight="1">
-      <c r="C108" s="42" t="inlineStr">
+    <row r="110" ht="72" customHeight="1">
+      <c r="C110" s="42" t="inlineStr">
         <is>
           <t>SELECT ja_id
 FROM m_ja
@@ -9299,64 +9812,64 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
-      <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
-      <c r="J108" s="10" t="n"/>
-      <c r="K108" s="10" t="n"/>
-      <c r="L108" s="10" t="n"/>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="n"/>
-      <c r="O108" s="10" t="n"/>
-      <c r="P108" s="10" t="n"/>
-      <c r="Q108" s="10" t="n"/>
-      <c r="R108" s="10" t="n"/>
-      <c r="S108" s="10" t="n"/>
-      <c r="T108" s="10" t="n"/>
-      <c r="U108" s="10" t="n"/>
-      <c r="V108" s="10" t="n"/>
-      <c r="W108" s="10" t="n"/>
-      <c r="X108" s="10" t="n"/>
-      <c r="Y108" s="10" t="n"/>
-      <c r="Z108" s="10" t="n"/>
-      <c r="AA108" s="10" t="n"/>
-      <c r="AB108" s="10" t="n"/>
-      <c r="AC108" s="10" t="n"/>
-      <c r="AD108" s="10" t="n"/>
-      <c r="AE108" s="10" t="n"/>
-      <c r="AF108" s="10" t="n"/>
-      <c r="AG108" s="10" t="n"/>
-      <c r="AH108" s="10" t="n"/>
-      <c r="AI108" s="10" t="n"/>
-      <c r="AJ108" s="10" t="n"/>
-      <c r="AK108" s="11" t="n"/>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="10" t="n"/>
+      <c r="L110" s="10" t="n"/>
+      <c r="M110" s="10" t="n"/>
+      <c r="N110" s="10" t="n"/>
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="10" t="n"/>
+      <c r="R110" s="10" t="n"/>
+      <c r="S110" s="10" t="n"/>
+      <c r="T110" s="10" t="n"/>
+      <c r="U110" s="10" t="n"/>
+      <c r="V110" s="10" t="n"/>
+      <c r="W110" s="10" t="n"/>
+      <c r="X110" s="10" t="n"/>
+      <c r="Y110" s="10" t="n"/>
+      <c r="Z110" s="10" t="n"/>
+      <c r="AA110" s="10" t="n"/>
+      <c r="AB110" s="10" t="n"/>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="10" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="10" t="n"/>
+      <c r="AK110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
         <is>
           <t>存在しない場合：HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="B110" s="27" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="B112" s="27" t="inlineStr">
         <is>
           <t>4.5 管理支店コードの一意性チェック</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="36" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
+    <row r="113" ht="36" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
         <is>
           <t>`kanri_shiten_code` が `m_kanri_shiten` テーブルに既に存在しないことを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="72" customHeight="1">
-      <c r="C112" s="42" t="inlineStr">
+    <row r="114" ht="72" customHeight="1">
+      <c r="C114" s="42" t="inlineStr">
         <is>
           <t>SELECT kanri_shiten_id
 FROM m_kanri_shiten
@@ -9364,64 +9877,64 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="n"/>
-      <c r="O112" s="10" t="n"/>
-      <c r="P112" s="10" t="n"/>
-      <c r="Q112" s="10" t="n"/>
-      <c r="R112" s="10" t="n"/>
-      <c r="S112" s="10" t="n"/>
-      <c r="T112" s="10" t="n"/>
-      <c r="U112" s="10" t="n"/>
-      <c r="V112" s="10" t="n"/>
-      <c r="W112" s="10" t="n"/>
-      <c r="X112" s="10" t="n"/>
-      <c r="Y112" s="10" t="n"/>
-      <c r="Z112" s="10" t="n"/>
-      <c r="AA112" s="10" t="n"/>
-      <c r="AB112" s="10" t="n"/>
-      <c r="AC112" s="10" t="n"/>
-      <c r="AD112" s="10" t="n"/>
-      <c r="AE112" s="10" t="n"/>
-      <c r="AF112" s="10" t="n"/>
-      <c r="AG112" s="10" t="n"/>
-      <c r="AH112" s="10" t="n"/>
-      <c r="AI112" s="10" t="n"/>
-      <c r="AJ112" s="10" t="n"/>
-      <c r="AK112" s="11" t="n"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="C113" s="41" t="inlineStr">
-        <is>
-          <t>既に存在する場合：HTTP 409 Conflict を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="B114" s="27" t="inlineStr">
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="36" customHeight="1">
+      <c r="C115" s="41" t="inlineStr">
+        <is>
+          <t>既に存在する場合：HTTP 400 (`DUPLICATE_CODE`) を返却する（`管理支店コード「{kanri_shiten_code}」はすでに登録されています。`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="B116" s="27" t="inlineStr">
         <is>
           <t>4.6 データ登録</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="C115" s="41" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="C117" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して新規レコードを登録する。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="234" customHeight="1">
-      <c r="C116" s="42" t="inlineStr">
+    <row r="118" ht="234" customHeight="1">
+      <c r="C118" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO m_kanri_shiten (
   ja_id, kanri_shiten_code, kanri_shiten_name, kanri_shiten_name_kana,
@@ -9438,57 +9951,57 @@
 RETURNING kanri_shiten_id</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
-      <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
-      <c r="J116" s="10" t="n"/>
-      <c r="K116" s="10" t="n"/>
-      <c r="L116" s="10" t="n"/>
-      <c r="M116" s="10" t="n"/>
-      <c r="N116" s="10" t="n"/>
-      <c r="O116" s="10" t="n"/>
-      <c r="P116" s="10" t="n"/>
-      <c r="Q116" s="10" t="n"/>
-      <c r="R116" s="10" t="n"/>
-      <c r="S116" s="10" t="n"/>
-      <c r="T116" s="10" t="n"/>
-      <c r="U116" s="10" t="n"/>
-      <c r="V116" s="10" t="n"/>
-      <c r="W116" s="10" t="n"/>
-      <c r="X116" s="10" t="n"/>
-      <c r="Y116" s="10" t="n"/>
-      <c r="Z116" s="10" t="n"/>
-      <c r="AA116" s="10" t="n"/>
-      <c r="AB116" s="10" t="n"/>
-      <c r="AC116" s="10" t="n"/>
-      <c r="AD116" s="10" t="n"/>
-      <c r="AE116" s="10" t="n"/>
-      <c r="AF116" s="10" t="n"/>
-      <c r="AG116" s="10" t="n"/>
-      <c r="AH116" s="10" t="n"/>
-      <c r="AI116" s="10" t="n"/>
-      <c r="AJ116" s="10" t="n"/>
-      <c r="AK116" s="11" t="n"/>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="B117" s="27" t="inlineStr">
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="10" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="10" t="n"/>
+      <c r="J118" s="10" t="n"/>
+      <c r="K118" s="10" t="n"/>
+      <c r="L118" s="10" t="n"/>
+      <c r="M118" s="10" t="n"/>
+      <c r="N118" s="10" t="n"/>
+      <c r="O118" s="10" t="n"/>
+      <c r="P118" s="10" t="n"/>
+      <c r="Q118" s="10" t="n"/>
+      <c r="R118" s="10" t="n"/>
+      <c r="S118" s="10" t="n"/>
+      <c r="T118" s="10" t="n"/>
+      <c r="U118" s="10" t="n"/>
+      <c r="V118" s="10" t="n"/>
+      <c r="W118" s="10" t="n"/>
+      <c r="X118" s="10" t="n"/>
+      <c r="Y118" s="10" t="n"/>
+      <c r="Z118" s="10" t="n"/>
+      <c r="AA118" s="10" t="n"/>
+      <c r="AB118" s="10" t="n"/>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="10" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="10" t="n"/>
+      <c r="AK118" s="11" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="B119" s="27" t="inlineStr">
         <is>
           <t>4.7 操作ログの記録</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="C118" s="41" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="C120" s="41" t="inlineStr">
         <is>
           <t>`t_log` テーブルに操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="180" customHeight="1">
-      <c r="C119" s="42" t="inlineStr">
+    <row r="121" ht="180" customHeight="1">
+      <c r="C121" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (
   log_type, log_datetime, account_id, ja_id,
@@ -9497,381 +10010,520 @@
 )
 VALUES (
   1, NOW(), :user_account_id, :ja_id,
-  '管理支店マスタ登録画面', 'KANRI_SHITEN_CREATE', 1,
+  '管理支店マスタ登録画面(ACSMS-SCR-009)', 'CREATE', 1,
   :new_kanri_shiten_id, 'm_kanri_shiten', :after_value_json, :ip_address, :user_agent
 )</t>
         </is>
       </c>
-      <c r="D119" s="10" t="n"/>
-      <c r="E119" s="10" t="n"/>
-      <c r="F119" s="10" t="n"/>
-      <c r="G119" s="10" t="n"/>
-      <c r="H119" s="10" t="n"/>
-      <c r="I119" s="10" t="n"/>
-      <c r="J119" s="10" t="n"/>
-      <c r="K119" s="10" t="n"/>
-      <c r="L119" s="10" t="n"/>
-      <c r="M119" s="10" t="n"/>
-      <c r="N119" s="10" t="n"/>
-      <c r="O119" s="10" t="n"/>
-      <c r="P119" s="10" t="n"/>
-      <c r="Q119" s="10" t="n"/>
-      <c r="R119" s="10" t="n"/>
-      <c r="S119" s="10" t="n"/>
-      <c r="T119" s="10" t="n"/>
-      <c r="U119" s="10" t="n"/>
-      <c r="V119" s="10" t="n"/>
-      <c r="W119" s="10" t="n"/>
-      <c r="X119" s="10" t="n"/>
-      <c r="Y119" s="10" t="n"/>
-      <c r="Z119" s="10" t="n"/>
-      <c r="AA119" s="10" t="n"/>
-      <c r="AB119" s="10" t="n"/>
-      <c r="AC119" s="10" t="n"/>
-      <c r="AD119" s="10" t="n"/>
-      <c r="AE119" s="10" t="n"/>
-      <c r="AF119" s="10" t="n"/>
-      <c r="AG119" s="10" t="n"/>
-      <c r="AH119" s="10" t="n"/>
-      <c r="AI119" s="10" t="n"/>
-      <c r="AJ119" s="10" t="n"/>
-      <c r="AK119" s="11" t="n"/>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="B120" s="27" t="inlineStr">
-        <is>
-          <t>4.8 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="C121" s="41" t="inlineStr">
-        <is>
-          <t>登録した管理支店データと成功メッセージを JSON 形式で返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="C122" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 201 Created</t>
-        </is>
-      </c>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="10" t="n"/>
+      <c r="J121" s="10" t="n"/>
+      <c r="K121" s="10" t="n"/>
+      <c r="L121" s="10" t="n"/>
+      <c r="M121" s="10" t="n"/>
+      <c r="N121" s="10" t="n"/>
+      <c r="O121" s="10" t="n"/>
+      <c r="P121" s="10" t="n"/>
+      <c r="Q121" s="10" t="n"/>
+      <c r="R121" s="10" t="n"/>
+      <c r="S121" s="10" t="n"/>
+      <c r="T121" s="10" t="n"/>
+      <c r="U121" s="10" t="n"/>
+      <c r="V121" s="10" t="n"/>
+      <c r="W121" s="10" t="n"/>
+      <c r="X121" s="10" t="n"/>
+      <c r="Y121" s="10" t="n"/>
+      <c r="Z121" s="10" t="n"/>
+      <c r="AA121" s="10" t="n"/>
+      <c r="AB121" s="10" t="n"/>
+      <c r="AC121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="10" t="n"/>
+      <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="10" t="n"/>
+      <c r="AK121" s="11" t="n"/>
+    </row>
+    <row r="122" ht="324" customHeight="1">
+      <c r="C122" s="42" t="inlineStr">
+        <is>
+          <t>before_value は INSERT のため空文字列を設定する。
+after_value：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "kanri_shiten_id": 2,
+  "ja_id": 1,
+  "kanri_shiten_code": "113-3300-002",
+  "kanri_shiten_name": "東京第二支店",
+  "kanri_shiten_name_kana": "ﾄｳｷｮｳﾀﾞｲﾆｼﾃﾝ",
+  "todofuken_code": "13",
+  "yubin_no": "1000002",
+  "address": "千代田区千代田2-2-2",
+  "tel": "0312345680",
+  "fax": "0312345681",
+  "paper_flg": true,
+  "denshi_flg": true,
+  "biko": "新規登録テスト"
+}</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="10" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="10" t="n"/>
+      <c r="I122" s="10" t="n"/>
+      <c r="J122" s="10" t="n"/>
+      <c r="K122" s="10" t="n"/>
+      <c r="L122" s="10" t="n"/>
+      <c r="M122" s="10" t="n"/>
+      <c r="N122" s="10" t="n"/>
+      <c r="O122" s="10" t="n"/>
+      <c r="P122" s="10" t="n"/>
+      <c r="Q122" s="10" t="n"/>
+      <c r="R122" s="10" t="n"/>
+      <c r="S122" s="10" t="n"/>
+      <c r="T122" s="10" t="n"/>
+      <c r="U122" s="10" t="n"/>
+      <c r="V122" s="10" t="n"/>
+      <c r="W122" s="10" t="n"/>
+      <c r="X122" s="10" t="n"/>
+      <c r="Y122" s="10" t="n"/>
+      <c r="Z122" s="10" t="n"/>
+      <c r="AA122" s="10" t="n"/>
+      <c r="AB122" s="10" t="n"/>
+      <c r="AC122" s="10" t="n"/>
+      <c r="AD122" s="10" t="n"/>
+      <c r="AE122" s="10" t="n"/>
+      <c r="AF122" s="10" t="n"/>
+      <c r="AG122" s="10" t="n"/>
+      <c r="AH122" s="10" t="n"/>
+      <c r="AI122" s="10" t="n"/>
+      <c r="AJ122" s="10" t="n"/>
+      <c r="AK122" s="11" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="B123" s="27" t="inlineStr">
         <is>
-          <t>4.9 例外処理</t>
+          <t>4.8 レスポンス生成</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="C124" s="41" t="inlineStr">
         <is>
+          <t>登録した管理支店データと成功メッセージを JSON 形式で返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="C125" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 201 Created</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>4.9 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="C127" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 Internal Server Error を返却する。</t>
         </is>
       </c>
     </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="C128" s="41" t="inlineStr">
+        <is>
+          <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="288" customHeight="1">
+      <c r="C129" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (
+  log_type, log_datetime, account_id, ja_id,
+  gamen_name, operation, result_status,
+  target_id, target_table,
+  before_value, after_value,
+  error_message, stack_trace,
+  ip_address, user_agent
+)
+VALUES (
+  3, NOW(), :user_account_id, :ja_id,
+  '管理支店マスタ登録画面(ACSMS-SCR-009)', 'CREATE', 2,
+  NULL, 'm_kanri_shiten',
+  '', '',
+  :error_message, :stack_trace,
+  :ip_address, :user_agent
+)</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="10" t="n"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
+      <c r="H129" s="10" t="n"/>
+      <c r="I129" s="10" t="n"/>
+      <c r="J129" s="10" t="n"/>
+      <c r="K129" s="10" t="n"/>
+      <c r="L129" s="10" t="n"/>
+      <c r="M129" s="10" t="n"/>
+      <c r="N129" s="10" t="n"/>
+      <c r="O129" s="10" t="n"/>
+      <c r="P129" s="10" t="n"/>
+      <c r="Q129" s="10" t="n"/>
+      <c r="R129" s="10" t="n"/>
+      <c r="S129" s="10" t="n"/>
+      <c r="T129" s="10" t="n"/>
+      <c r="U129" s="10" t="n"/>
+      <c r="V129" s="10" t="n"/>
+      <c r="W129" s="10" t="n"/>
+      <c r="X129" s="10" t="n"/>
+      <c r="Y129" s="10" t="n"/>
+      <c r="Z129" s="10" t="n"/>
+      <c r="AA129" s="10" t="n"/>
+      <c r="AB129" s="10" t="n"/>
+      <c r="AC129" s="10" t="n"/>
+      <c r="AD129" s="10" t="n"/>
+      <c r="AE129" s="10" t="n"/>
+      <c r="AF129" s="10" t="n"/>
+      <c r="AG129" s="10" t="n"/>
+      <c r="AH129" s="10" t="n"/>
+      <c r="AI129" s="10" t="n"/>
+      <c r="AJ129" s="10" t="n"/>
+      <c r="AK129" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="298">
-    <mergeCell ref="B102:AK102"/>
+  <mergeCells count="317">
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="T53:X53"/>
+    <mergeCell ref="D56:L56"/>
+    <mergeCell ref="C128:AK128"/>
+    <mergeCell ref="T55:X55"/>
+    <mergeCell ref="C113:AK113"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C129:AK129"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="Y53:AE53"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="B14:I18"/>
+    <mergeCell ref="Y55:AE55"/>
+    <mergeCell ref="C117:AK117"/>
+    <mergeCell ref="T40:X40"/>
+    <mergeCell ref="C115:AK115"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="T45:X45"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="Y33:AB33"/>
+    <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="Y56:AE56"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="D94:AK94"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="B108:AK108"/>
+    <mergeCell ref="C63:AK63"/>
+    <mergeCell ref="T51:X51"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="Q54:S54"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="B98:AK98"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="Y38:AE38"/>
+    <mergeCell ref="Q57:S57"/>
+    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="Y51:AE51"/>
+    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="D95:AK95"/>
+    <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="B126:AK126"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Y22:AB22"/>
+    <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="M46:P46"/>
+    <mergeCell ref="D97:AK97"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="T22:X22"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B119:AK119"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="B112:AK112"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="C118:AK118"/>
+    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="T46:X46"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="D49:L49"/>
+    <mergeCell ref="T48:X48"/>
+    <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="A20:AK20"/>
+    <mergeCell ref="AF42:AK42"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="D54:L54"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="T56:X56"/>
+    <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="T43:X43"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="C111:AK111"/>
+    <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="B82:AK82"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="B83:AK83"/>
+    <mergeCell ref="C124:AK124"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D44:L44"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="B62:I62"/>
     <mergeCell ref="D87:AK87"/>
-    <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="T33:X33"/>
-    <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="D48:L48"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C109:AK109"/>
+    <mergeCell ref="C84:AK84"/>
+    <mergeCell ref="C127:AK127"/>
+    <mergeCell ref="Y54:AE54"/>
+    <mergeCell ref="C114:AK114"/>
+    <mergeCell ref="A36:AK36"/>
+    <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T28:X28"/>
+    <mergeCell ref="T30:X30"/>
+    <mergeCell ref="T57:X57"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="D53:L53"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="T54:X54"/>
+    <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AD2:AG3"/>
+    <mergeCell ref="D88:AK88"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C40:C56"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="D90:AK90"/>
+    <mergeCell ref="J13:AK13"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="B104:AK104"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C122:AK122"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="C125:AK125"/>
+    <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="Y57:AE57"/>
+    <mergeCell ref="T42:X42"/>
+    <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="T50:X50"/>
+    <mergeCell ref="A81:AK81"/>
+    <mergeCell ref="T44:X44"/>
+    <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="C105:AK105"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="C120:AK120"/>
+    <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="D91:AK91"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="AF46:AK46"/>
+    <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="AF48:AK48"/>
+    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="Y32:AB32"/>
-    <mergeCell ref="T53:X53"/>
-    <mergeCell ref="C108:AK108"/>
-    <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="M46:P46"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D82:AK82"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="Y52:AE52"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="T55:X55"/>
-    <mergeCell ref="C113:AK113"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="N19:AK19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C112:AK112"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="AF29:AK29"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C94:AK94"/>
-    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D51:L51"/>
-    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="Y54:AE54"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="M35:P35"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="J2:P3"/>
-    <mergeCell ref="B114:AK114"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="B123:AK123"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="C70:AK70"/>
-    <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="A37:AK37"/>
-    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="M45:P45"/>
-    <mergeCell ref="T30:X30"/>
-    <mergeCell ref="A21:AK21"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="C39:L39"/>
-    <mergeCell ref="T29:X29"/>
-    <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="B117:AK117"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="D53:L53"/>
     <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="AC29:AE29"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
-    <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
-    <mergeCell ref="T54:X54"/>
-    <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="D89:AK89"/>
-    <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="Z2:AC3"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="AF41:AK41"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="B116:AK116"/>
     <mergeCell ref="M44:P44"/>
-    <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="D88:AK88"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
-    <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="C99:AK99"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="T40:X40"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="C35:L35"/>
-    <mergeCell ref="M51:P51"/>
-    <mergeCell ref="D90:AK90"/>
-    <mergeCell ref="C118:AK118"/>
-    <mergeCell ref="J13:AK13"/>
-    <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C115:AK115"/>
+    <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="C55:L55"/>
-    <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B106:AK106"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="T46:X46"/>
-    <mergeCell ref="C122:AK122"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q51:S51"/>
-    <mergeCell ref="M27:P27"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
-    <mergeCell ref="D49:L49"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="Y27:AB27"/>
-    <mergeCell ref="T48:X48"/>
-    <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="T45:X45"/>
-    <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="Y33:AB33"/>
-    <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="T42:X42"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="D102:AK102"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
-    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="D92:AK92"/>
-    <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="Q49:S49"/>
-    <mergeCell ref="T50:X50"/>
     <mergeCell ref="C107:AK107"/>
-    <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C64:AK64"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="C73:AK73"/>
-    <mergeCell ref="J8:AK8"/>
     <mergeCell ref="M55:P55"/>
-    <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="AF40:AK40"/>
-    <mergeCell ref="M49:P49"/>
     <mergeCell ref="C121:AK121"/>
-    <mergeCell ref="M39:P39"/>
     <mergeCell ref="M48:P48"/>
-    <mergeCell ref="T51:X51"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="T41:X41"/>
-    <mergeCell ref="C105:AK105"/>
-    <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="B80:AK80"/>
-    <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="AC32:AE32"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="T43:X43"/>
-    <mergeCell ref="C119:AK119"/>
-    <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
-    <mergeCell ref="C116:AK116"/>
-    <mergeCell ref="C41:C54"/>
+    <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
-    <mergeCell ref="N16:AK16"/>
-    <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="Q54:S54"/>
-    <mergeCell ref="Q55:S55"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="C67:AK67"/>
-    <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="D91:AK91"/>
-    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B96:AK96"/>
-    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
-    <mergeCell ref="B14:I19"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q40:S40"/>
     <mergeCell ref="T49:X49"/>
-    <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="D93:AK93"/>
-    <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
-    <mergeCell ref="B120:AK120"/>
-    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="Y42:AE42"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="J14:M14"/>
     <mergeCell ref="D85:AK85"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="M52:P52"/>
-    <mergeCell ref="D100:AK100"/>
-    <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="C124:AK124"/>
-    <mergeCell ref="AF46:AK46"/>
-    <mergeCell ref="AF28:AK28"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="Y35:AB35"/>
-    <mergeCell ref="D50:L50"/>
-    <mergeCell ref="D44:L44"/>
-    <mergeCell ref="Q53:S53"/>
-    <mergeCell ref="D84:AK84"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="Y51:AE51"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="A79:AK79"/>
-    <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="B110:AK110"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="D86:AK86"/>
-    <mergeCell ref="C40:L40"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="M30:P30"/>
-    <mergeCell ref="D95:AK95"/>
-    <mergeCell ref="Q52:S52"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="AF29:AK29"/>
-    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="C110:AK110"/>
+    <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9883,7 +10535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK121"/>
+  <dimension ref="A1:AK133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -10044,7 +10696,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10451,7 +11103,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常に管理支店を更新しました</t>
+          <t>更新しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -11761,7 +12413,7 @@
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_code</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -11805,7 +12457,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>管理支店コード</t>
+          <t>JA名（m_jaからJOIN）</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -11821,7 +12473,7 @@
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>kanri_shiten_code</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -11865,7 +12517,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>管理支店名</t>
+          <t>管理支店コード</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -11881,7 +12533,7 @@
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name_kana</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -11914,7 +12566,7 @@
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z45" s="10" t="n"/>
@@ -11925,7 +12577,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>管理支店名（カナ）</t>
+          <t>管理支店名</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -11941,7 +12593,7 @@
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>kanri_shiten_name_kana</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -11985,7 +12637,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード</t>
+          <t>管理支店名（カナ）</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -12001,7 +12653,7 @@
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -12034,7 +12686,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -12045,7 +12697,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>都道府県コード</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -12061,7 +12713,7 @@
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -12094,7 +12746,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -12105,7 +12757,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>都道府県名（m_todofukenからJOIN）</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -12121,7 +12773,7 @@
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -12154,7 +12806,7 @@
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z49" s="10" t="n"/>
@@ -12165,7 +12817,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -12181,7 +12833,7 @@
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -12214,7 +12866,7 @@
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z50" s="10" t="n"/>
@@ -12225,7 +12877,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -12241,7 +12893,7 @@
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -12254,7 +12906,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -12285,7 +12937,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -12301,7 +12953,7 @@
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -12314,7 +12966,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -12345,7 +12997,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -12361,7 +13013,7 @@
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -12374,7 +13026,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -12394,7 +13046,7 @@
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z53" s="10" t="n"/>
@@ -12405,7 +13057,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>紙版取扱フラグ</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -12421,7 +13073,7 @@
       <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>denshi_flg</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -12434,7 +13086,7 @@
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N54" s="10" t="n"/>
@@ -12447,11 +13099,7 @@
       </c>
       <c r="R54" s="10" t="n"/>
       <c r="S54" s="11" t="n"/>
-      <c r="T54" s="17" t="inlineStr">
-        <is>
-          <t>ISO 8601</t>
-        </is>
-      </c>
+      <c r="T54" s="17" t="inlineStr"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
       <c r="W54" s="10" t="n"/>
@@ -12469,7 +13117,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>電子版取扱フラグ</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -12482,10 +13130,10 @@
       <c r="B55" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="C55" s="39" t="n"/>
+      <c r="C55" s="38" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -12511,11 +13159,7 @@
       </c>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr">
-        <is>
-          <t>ISO 8601</t>
-        </is>
-      </c>
+      <c r="T55" s="17" t="inlineStr"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
@@ -12533,7 +13177,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -12546,12 +13190,12 @@
       <c r="B56" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
       <c r="E56" s="10" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
@@ -12575,7 +13219,11 @@
       </c>
       <c r="R56" s="10" t="n"/>
       <c r="S56" s="11" t="n"/>
-      <c r="T56" s="17" t="inlineStr"/>
+      <c r="T56" s="17" t="inlineStr">
+        <is>
+          <t>ISO 8601</t>
+        </is>
+      </c>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
       <c r="W56" s="10" t="n"/>
@@ -12593,7 +13241,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>処理結果メッセージ</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -12602,22 +13250,146 @@
       <c r="AJ56" s="10" t="n"/>
       <c r="AK56" s="11" t="n"/>
     </row>
-    <row r="57" ht="19.5" customHeight="1"/>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="B58" s="40" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="11" t="n"/>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="17" t="inlineStr">
+        <is>
+          <t>ISO 8601</t>
+        </is>
+      </c>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="11" t="n"/>
+      <c r="Y57" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="11" t="n"/>
+      <c r="AF57" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="11" t="n"/>
+      <c r="M58" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="11" t="n"/>
+      <c r="T58" s="17" t="inlineStr"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="11" t="n"/>
+      <c r="Y58" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="11" t="n"/>
+      <c r="AF58" s="19" t="inlineStr">
+        <is>
+          <t>処理結果メッセージ</t>
+        </is>
+      </c>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1"/>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="270" customHeight="1">
-      <c r="C59" s="19" t="inlineStr">
+    <row r="61" ht="270" customHeight="1">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>PUT /api/v1/kanri-shiten/1
 Content-Type: application/json
 {
   "kanri_shiten_name": "東京中央会支店（改称）",
-  "kanri_shiten_name_kana": "トウキョウチュウオウカイシテン（カイショウ）",
+  "kanri_shiten_name_kana": "ﾄｳｷｮｳﾁｭｳｵｳｶｲｼﾃﾝ ｶｲｼｮｳ",
   "todofuken_code": "13",
   "yubin_no": "1000001",
   "address": "千代田区千代田1-1-1 改修ビル3F",
@@ -12629,59 +13401,61 @@
 }</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n"/>
-      <c r="E59" s="10" t="n"/>
-      <c r="F59" s="10" t="n"/>
-      <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="10" t="n"/>
-      <c r="M59" s="10" t="n"/>
-      <c r="N59" s="10" t="n"/>
-      <c r="O59" s="10" t="n"/>
-      <c r="P59" s="10" t="n"/>
-      <c r="Q59" s="10" t="n"/>
-      <c r="R59" s="10" t="n"/>
-      <c r="S59" s="10" t="n"/>
-      <c r="T59" s="10" t="n"/>
-      <c r="U59" s="10" t="n"/>
-      <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n"/>
-      <c r="X59" s="10" t="n"/>
-      <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="10" t="n"/>
-      <c r="AA59" s="10" t="n"/>
-      <c r="AB59" s="10" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="10" t="n"/>
-      <c r="AF59" s="10" t="n"/>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="10" t="n"/>
-      <c r="AK59" s="11" t="n"/>
-    </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="B61" s="40" t="inlineStr">
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="10" t="n"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="10" t="n"/>
+      <c r="AF61" s="10" t="n"/>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="360" customHeight="1">
-      <c r="C62" s="19" t="inlineStr">
+    <row r="64" ht="396" customHeight="1">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
     "kanri_shiten_id": 1,
     "ja_id": 1,
+    "ja_name": "JA東京",
     "kanri_shiten_code": "113-3300-001",
     "kanri_shiten_name": "東京中央会支店（改称）",
-    "kanri_shiten_name_kana": "トウキョウチュウオウカイシテン（カイショウ）",
+    "kanri_shiten_name_kana": "ﾄｳｷｮｳﾁｭｳｵｳｶｲｼﾃﾝ ｶｲｼｮｳ",
     "todofuken_code": "13",
+    "todofuken_name": "東京都",
     "yubin_no": "1000001",
     "address": "千代田区千代田1-1-1 改修ビル3F",
     "tel": "0312345678",
@@ -12692,54 +13466,54 @@
     "created_at": "2026-01-15T10:00:00Z",
     "updated_at": "2026-04-07T14:30:00Z"
   },
-  "message": "管理支店を更新しました"
+  "message": "更新しました。"
 }</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n"/>
-      <c r="E62" s="10" t="n"/>
-      <c r="F62" s="10" t="n"/>
-      <c r="G62" s="10" t="n"/>
-      <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="n"/>
-      <c r="J62" s="10" t="n"/>
-      <c r="K62" s="10" t="n"/>
-      <c r="L62" s="10" t="n"/>
-      <c r="M62" s="10" t="n"/>
-      <c r="N62" s="10" t="n"/>
-      <c r="O62" s="10" t="n"/>
-      <c r="P62" s="10" t="n"/>
-      <c r="Q62" s="10" t="n"/>
-      <c r="R62" s="10" t="n"/>
-      <c r="S62" s="10" t="n"/>
-      <c r="T62" s="10" t="n"/>
-      <c r="U62" s="10" t="n"/>
-      <c r="V62" s="10" t="n"/>
-      <c r="W62" s="10" t="n"/>
-      <c r="X62" s="10" t="n"/>
-      <c r="Y62" s="10" t="n"/>
-      <c r="Z62" s="10" t="n"/>
-      <c r="AA62" s="10" t="n"/>
-      <c r="AB62" s="10" t="n"/>
-      <c r="AC62" s="10" t="n"/>
-      <c r="AD62" s="10" t="n"/>
-      <c r="AE62" s="10" t="n"/>
-      <c r="AF62" s="10" t="n"/>
-      <c r="AG62" s="10" t="n"/>
-      <c r="AH62" s="10" t="n"/>
-      <c r="AI62" s="10" t="n"/>
-      <c r="AJ62" s="10" t="n"/>
-      <c r="AK62" s="11" t="n"/>
-    </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="B64" s="40" t="inlineStr">
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="11" t="n"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="126" customHeight="1">
-      <c r="C65" s="19" t="inlineStr">
+    <row r="67" ht="126" customHeight="1">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -12750,50 +13524,50 @@
 }</t>
         </is>
       </c>
-      <c r="D65" s="10" t="n"/>
-      <c r="E65" s="10" t="n"/>
-      <c r="F65" s="10" t="n"/>
-      <c r="G65" s="10" t="n"/>
-      <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="10" t="n"/>
-      <c r="M65" s="10" t="n"/>
-      <c r="N65" s="10" t="n"/>
-      <c r="O65" s="10" t="n"/>
-      <c r="P65" s="10" t="n"/>
-      <c r="Q65" s="10" t="n"/>
-      <c r="R65" s="10" t="n"/>
-      <c r="S65" s="10" t="n"/>
-      <c r="T65" s="10" t="n"/>
-      <c r="U65" s="10" t="n"/>
-      <c r="V65" s="10" t="n"/>
-      <c r="W65" s="10" t="n"/>
-      <c r="X65" s="10" t="n"/>
-      <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="10" t="n"/>
-      <c r="AA65" s="10" t="n"/>
-      <c r="AB65" s="10" t="n"/>
-      <c r="AC65" s="10" t="n"/>
-      <c r="AD65" s="10" t="n"/>
-      <c r="AE65" s="10" t="n"/>
-      <c r="AF65" s="10" t="n"/>
-      <c r="AG65" s="10" t="n"/>
-      <c r="AH65" s="10" t="n"/>
-      <c r="AI65" s="10" t="n"/>
-      <c r="AJ65" s="10" t="n"/>
-      <c r="AK65" s="11" t="n"/>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="B67" s="40" t="inlineStr">
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="10" t="n"/>
+      <c r="X67" s="10" t="n"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="10" t="n"/>
+      <c r="AE67" s="10" t="n"/>
+      <c r="AF67" s="10" t="n"/>
+      <c r="AG67" s="10" t="n"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="10" t="n"/>
+      <c r="AJ67" s="10" t="n"/>
+      <c r="AK67" s="11" t="n"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="72" customHeight="1">
-      <c r="C68" s="19" t="inlineStr">
+    <row r="70" ht="72" customHeight="1">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -12801,50 +13575,50 @@
 }</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="10" t="n"/>
-      <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n"/>
-      <c r="J68" s="10" t="n"/>
-      <c r="K68" s="10" t="n"/>
-      <c r="L68" s="10" t="n"/>
-      <c r="M68" s="10" t="n"/>
-      <c r="N68" s="10" t="n"/>
-      <c r="O68" s="10" t="n"/>
-      <c r="P68" s="10" t="n"/>
-      <c r="Q68" s="10" t="n"/>
-      <c r="R68" s="10" t="n"/>
-      <c r="S68" s="10" t="n"/>
-      <c r="T68" s="10" t="n"/>
-      <c r="U68" s="10" t="n"/>
-      <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n"/>
-      <c r="X68" s="10" t="n"/>
-      <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="10" t="n"/>
-      <c r="AA68" s="10" t="n"/>
-      <c r="AB68" s="10" t="n"/>
-      <c r="AC68" s="10" t="n"/>
-      <c r="AD68" s="10" t="n"/>
-      <c r="AE68" s="10" t="n"/>
-      <c r="AF68" s="10" t="n"/>
-      <c r="AG68" s="10" t="n"/>
-      <c r="AH68" s="10" t="n"/>
-      <c r="AI68" s="10" t="n"/>
-      <c r="AJ68" s="10" t="n"/>
-      <c r="AK68" s="11" t="n"/>
-    </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="B70" s="40" t="inlineStr">
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
+      <c r="AF70" s="10" t="n"/>
+      <c r="AG70" s="10" t="n"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="10" t="n"/>
+      <c r="AJ70" s="10" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="72" customHeight="1">
-      <c r="C71" s="19" t="inlineStr">
+    <row r="73" ht="72" customHeight="1">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -12852,50 +13626,50 @@
 }</t>
         </is>
       </c>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="10" t="n"/>
-      <c r="U71" s="10" t="n"/>
-      <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="10" t="n"/>
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-      <c r="AA71" s="10" t="n"/>
-      <c r="AB71" s="10" t="n"/>
-      <c r="AC71" s="10" t="n"/>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="10" t="n"/>
-      <c r="AF71" s="10" t="n"/>
-      <c r="AG71" s="10" t="n"/>
-      <c r="AH71" s="10" t="n"/>
-      <c r="AI71" s="10" t="n"/>
-      <c r="AJ71" s="10" t="n"/>
-      <c r="AK71" s="11" t="n"/>
-    </row>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="B73" s="40" t="inlineStr">
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="11" t="n"/>
+    </row>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="B75" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="72" customHeight="1">
-      <c r="C74" s="19" t="inlineStr">
+    <row r="76" ht="72" customHeight="1">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -12903,50 +13677,50 @@
 }</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n"/>
-      <c r="M74" s="10" t="n"/>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n"/>
-      <c r="R74" s="10" t="n"/>
-      <c r="S74" s="10" t="n"/>
-      <c r="T74" s="10" t="n"/>
-      <c r="U74" s="10" t="n"/>
-      <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n"/>
-      <c r="X74" s="10" t="n"/>
-      <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
-      <c r="AA74" s="10" t="n"/>
-      <c r="AB74" s="10" t="n"/>
-      <c r="AC74" s="10" t="n"/>
-      <c r="AD74" s="10" t="n"/>
-      <c r="AE74" s="10" t="n"/>
-      <c r="AF74" s="10" t="n"/>
-      <c r="AG74" s="10" t="n"/>
-      <c r="AH74" s="10" t="n"/>
-      <c r="AI74" s="10" t="n"/>
-      <c r="AJ74" s="10" t="n"/>
-      <c r="AK74" s="11" t="n"/>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="B76" s="40" t="inlineStr">
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="B78" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="72" customHeight="1">
-      <c r="C77" s="19" t="inlineStr">
+    <row r="79" ht="72" customHeight="1">
+      <c r="C79" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -12954,348 +13728,432 @@
 }</t>
         </is>
       </c>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-      <c r="G77" s="10" t="n"/>
-      <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="10" t="n"/>
-      <c r="M77" s="10" t="n"/>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n"/>
-      <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
-      <c r="T77" s="10" t="n"/>
-      <c r="U77" s="10" t="n"/>
-      <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n"/>
-      <c r="X77" s="10" t="n"/>
-      <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="10" t="n"/>
-      <c r="AA77" s="10" t="n"/>
-      <c r="AB77" s="10" t="n"/>
-      <c r="AC77" s="10" t="n"/>
-      <c r="AD77" s="10" t="n"/>
-      <c r="AE77" s="10" t="n"/>
-      <c r="AF77" s="10" t="n"/>
-      <c r="AG77" s="10" t="n"/>
-      <c r="AH77" s="10" t="n"/>
-      <c r="AI77" s="10" t="n"/>
-      <c r="AJ77" s="10" t="n"/>
-      <c r="AK77" s="11" t="n"/>
-    </row>
-    <row r="79" ht="19.5" customHeight="1"/>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="A80" s="27" t="inlineStr">
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1"/>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+    <row r="83" ht="54" customHeight="1">
+      <c r="B83" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>`kanri_shiten_id`：数値型チェック、必須チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>リクエストボディの全フィールドを検証する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="D85" s="41" t="inlineStr">
-        <is>
-          <t>`kanri_shiten_name`：必須、最大100文字</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>`kanri_shiten_name_kana`：任意、最大100文字</t>
+          <t>`kanri_shiten_id`：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="D87" s="41" t="inlineStr">
-        <is>
-          <t>`todofuken_code`：必須、2文字</t>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>リクエストボディの全フィールドを検証する：</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>`yubin_no`：任意、半角数字7桁</t>
+          <t>`kanri_shiten_name`：必須、最大100文字</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>`address`：任意、最大200文字</t>
+          <t>`kanri_shiten_name_kana`：任意、最大100文字、半角カタカナ・半角数字のみ</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>`tel`：任意、半角数字のみ、最大15文字</t>
+          <t>`todofuken_code`：必須、2文字</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="D91" s="41" t="inlineStr">
         <is>
-          <t>`fax`：任意、半角数字のみ、最大15文字</t>
+          <t>`yubin_no`：任意、半角数字7桁</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="D92" s="41" t="inlineStr">
         <is>
-          <t>`paper_flg`：任意、ブール値（デフォルト: false）</t>
+          <t>`address`：任意、最大200文字</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="D93" s="41" t="inlineStr">
         <is>
-          <t>`denshi_flg`：任意、ブール値（デフォルト: false）</t>
+          <t>`tel`：任意、半角数字のみ、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="D94" s="41" t="inlineStr">
         <is>
-          <t>`biko`：任意、最大500文字</t>
+          <t>`fax`：任意、半角数字のみ、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="D95" s="41" t="inlineStr">
+        <is>
+          <t>`paper_flg`：任意、ブール値（デフォルト: false）</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="D96" s="41" t="inlineStr">
         <is>
+          <t>`denshi_flg`：任意、ブール値（デフォルト: false）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="D98" s="41" t="inlineStr">
+        <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="C100" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`kanri-shiten.update` を保持しているか確認する。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="D101" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+      <c r="C101" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="B103" s="27" t="inlineStr">
-        <is>
-          <t>4.3 対象レコードの存在確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="36" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
+          <t>権限チェック：`kanri_shiten.update` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="D103" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN / CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="D104" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_ADMIN：全項目更新可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="D105" s="41" t="inlineStr">
+        <is>
+          <t>CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN：許可フィールドのみ更新可能（§4.5 参照）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden（ACSMS-MSG-009-006）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>4.3 対象レコードの存在確認 + データスコープ</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
         <is>
           <t>`kanri_shiten_id` が `m_kanri_shiten` テーブルに存在し、論理削除されていないことを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="72" customHeight="1">
-      <c r="C105" s="42" t="inlineStr">
-        <is>
-          <t>SELECT kanri_shiten_id
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
+        <is>
+          <t>同時にデータスコープ（画面定義§1.3）も適用：</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="162" customHeight="1">
+      <c r="C110" s="42" t="inlineStr">
+        <is>
+          <t>SELECT kanri_shiten_id, ja_id
 FROM m_kanri_shiten
 WHERE kanri_shiten_id = :kanri_shiten_id
-  AND deleted_at IS NULL</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
-      <c r="P105" s="10" t="n"/>
-      <c r="Q105" s="10" t="n"/>
-      <c r="R105" s="10" t="n"/>
-      <c r="S105" s="10" t="n"/>
-      <c r="T105" s="10" t="n"/>
-      <c r="U105" s="10" t="n"/>
-      <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
-      <c r="X105" s="10" t="n"/>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="10" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="10" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="10" t="n"/>
-      <c r="AK105" s="11" t="n"/>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
-        <is>
-          <t>存在しない場合：HTTP 404 Not Found を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="B107" s="27" t="inlineStr">
+  AND deleted_at IS NULL
+  AND (
+    :role = 'NICHINO_ADMIN'
+    OR (:role IN ('CHUOKAI', 'JA_HONTEN') AND ja_id = :session_ja_id)
+    OR (:role = 'JA_KANRI_SHITEN' AND ja_id = :session_ja_id AND kanri_shiten_id = :session_kanri_shiten_id)
+  )</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="10" t="n"/>
+      <c r="L110" s="10" t="n"/>
+      <c r="M110" s="10" t="n"/>
+      <c r="N110" s="10" t="n"/>
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="10" t="n"/>
+      <c r="R110" s="10" t="n"/>
+      <c r="S110" s="10" t="n"/>
+      <c r="T110" s="10" t="n"/>
+      <c r="U110" s="10" t="n"/>
+      <c r="V110" s="10" t="n"/>
+      <c r="W110" s="10" t="n"/>
+      <c r="X110" s="10" t="n"/>
+      <c r="Y110" s="10" t="n"/>
+      <c r="Z110" s="10" t="n"/>
+      <c r="AA110" s="10" t="n"/>
+      <c r="AB110" s="10" t="n"/>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="10" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="10" t="n"/>
+      <c r="AK110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
+        <is>
+          <t>存在しない／スコープ違反の場合：HTTP 404 Not Found（ACSMS-MSG-009-005）を返却する（行の存在を漏らさない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="B112" s="27" t="inlineStr">
         <is>
           <t>4.4 都道府県コードの存在検証</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="C108" s="41" t="inlineStr">
-        <is>
-          <t>`todofuken_code` が `m_todofuken` テーブルに存在することを確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="54" customHeight="1">
-      <c r="C109" s="42" t="inlineStr">
+    <row r="113" ht="54" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
+        <is>
+          <t>`todofuken_code` が `m_todofuken` テーブルに存在することを確認する（NICHINO_ADMIN のみ通る経路 — §4.5 の allow-list で他ロールは弾かれる）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="54" customHeight="1">
+      <c r="C114" s="42" t="inlineStr">
         <is>
           <t>SELECT todofuken_code
 FROM m_todofuken
 WHERE todofuken_code = :todofuken_code</t>
         </is>
       </c>
-      <c r="D109" s="10" t="n"/>
-      <c r="E109" s="10" t="n"/>
-      <c r="F109" s="10" t="n"/>
-      <c r="G109" s="10" t="n"/>
-      <c r="H109" s="10" t="n"/>
-      <c r="I109" s="10" t="n"/>
-      <c r="J109" s="10" t="n"/>
-      <c r="K109" s="10" t="n"/>
-      <c r="L109" s="10" t="n"/>
-      <c r="M109" s="10" t="n"/>
-      <c r="N109" s="10" t="n"/>
-      <c r="O109" s="10" t="n"/>
-      <c r="P109" s="10" t="n"/>
-      <c r="Q109" s="10" t="n"/>
-      <c r="R109" s="10" t="n"/>
-      <c r="S109" s="10" t="n"/>
-      <c r="T109" s="10" t="n"/>
-      <c r="U109" s="10" t="n"/>
-      <c r="V109" s="10" t="n"/>
-      <c r="W109" s="10" t="n"/>
-      <c r="X109" s="10" t="n"/>
-      <c r="Y109" s="10" t="n"/>
-      <c r="Z109" s="10" t="n"/>
-      <c r="AA109" s="10" t="n"/>
-      <c r="AB109" s="10" t="n"/>
-      <c r="AC109" s="10" t="n"/>
-      <c r="AD109" s="10" t="n"/>
-      <c r="AE109" s="10" t="n"/>
-      <c r="AF109" s="10" t="n"/>
-      <c r="AG109" s="10" t="n"/>
-      <c r="AH109" s="10" t="n"/>
-      <c r="AI109" s="10" t="n"/>
-      <c r="AJ109" s="10" t="n"/>
-      <c r="AK109" s="11" t="n"/>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="C110" s="41" t="inlineStr">
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="C115" s="41" t="inlineStr">
         <is>
           <t>存在しない場合：HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="27" t="inlineStr">
-        <is>
-          <t>4.5 データ更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="C112" s="41" t="inlineStr">
-        <is>
-          <t>以下のSQLを実行してレコードを更新する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="270" customHeight="1">
-      <c r="C113" s="42" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>4.5 フィールドレベル制限の適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="C117" s="41" t="inlineStr">
+        <is>
+          <t>許可されていないフィールドがリクエストボディに含まれていても、サーバー側で**サイレントに破棄**（リクエストは 200 で成功するが、該当フィールドは DB に反映されない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="36" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
+        <is>
+          <t>UI側は事前に該当フィールドを `:disabled` でグレーアウトすることで二重防御する（`.claude/rules/security.md §Layer 3` 参照）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>4.6 データ更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="36" customHeight="1">
+      <c r="C120" s="41" t="inlineStr">
+        <is>
+          <t>§4.5 で許可されたフィールドのみ UPDATE 文に含める。NICHINO_ADMIN 経路は以下の全項目更新：</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="270" customHeight="1">
+      <c r="C121" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_kanri_shiten
 SET kanri_shiten_name = :kanri_shiten_name,
@@ -13314,57 +14172,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
-      <c r="P113" s="10" t="n"/>
-      <c r="Q113" s="10" t="n"/>
-      <c r="R113" s="10" t="n"/>
-      <c r="S113" s="10" t="n"/>
-      <c r="T113" s="10" t="n"/>
-      <c r="U113" s="10" t="n"/>
-      <c r="V113" s="10" t="n"/>
-      <c r="W113" s="10" t="n"/>
-      <c r="X113" s="10" t="n"/>
-      <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="10" t="n"/>
-      <c r="AA113" s="10" t="n"/>
-      <c r="AB113" s="10" t="n"/>
-      <c r="AC113" s="10" t="n"/>
-      <c r="AD113" s="10" t="n"/>
-      <c r="AE113" s="10" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
-      <c r="AI113" s="10" t="n"/>
-      <c r="AJ113" s="10" t="n"/>
-      <c r="AK113" s="11" t="n"/>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="B114" s="27" t="inlineStr">
-        <is>
-          <t>4.6 操作ログの記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="C115" s="41" t="inlineStr">
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="10" t="n"/>
+      <c r="J121" s="10" t="n"/>
+      <c r="K121" s="10" t="n"/>
+      <c r="L121" s="10" t="n"/>
+      <c r="M121" s="10" t="n"/>
+      <c r="N121" s="10" t="n"/>
+      <c r="O121" s="10" t="n"/>
+      <c r="P121" s="10" t="n"/>
+      <c r="Q121" s="10" t="n"/>
+      <c r="R121" s="10" t="n"/>
+      <c r="S121" s="10" t="n"/>
+      <c r="T121" s="10" t="n"/>
+      <c r="U121" s="10" t="n"/>
+      <c r="V121" s="10" t="n"/>
+      <c r="W121" s="10" t="n"/>
+      <c r="X121" s="10" t="n"/>
+      <c r="Y121" s="10" t="n"/>
+      <c r="Z121" s="10" t="n"/>
+      <c r="AA121" s="10" t="n"/>
+      <c r="AB121" s="10" t="n"/>
+      <c r="AC121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="10" t="n"/>
+      <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="10" t="n"/>
+      <c r="AK121" s="11" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>4.7 操作ログの記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="41" t="inlineStr">
         <is>
           <t>`t_log` テーブルに操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="180" customHeight="1">
-      <c r="C116" s="42" t="inlineStr">
+    <row r="124" ht="180" customHeight="1">
+      <c r="C124" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (
   log_type, log_datetime, account_id, ja_id,
@@ -13373,383 +14231,580 @@
 )
 VALUES (
   1, NOW(), :user_account_id, :ja_id,
-  '管理支店マスタ登録画面', 'KANRI_SHITEN_UPDATE', 1,
+  '管理支店マスタ登録画面(ACSMS-SCR-009)', 'UPDATE', 1,
   :kanri_shiten_id, 'm_kanri_shiten', :before_value_json, :after_value_json, :ip_address, :user_agent
 )</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
-      <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
-      <c r="J116" s="10" t="n"/>
-      <c r="K116" s="10" t="n"/>
-      <c r="L116" s="10" t="n"/>
-      <c r="M116" s="10" t="n"/>
-      <c r="N116" s="10" t="n"/>
-      <c r="O116" s="10" t="n"/>
-      <c r="P116" s="10" t="n"/>
-      <c r="Q116" s="10" t="n"/>
-      <c r="R116" s="10" t="n"/>
-      <c r="S116" s="10" t="n"/>
-      <c r="T116" s="10" t="n"/>
-      <c r="U116" s="10" t="n"/>
-      <c r="V116" s="10" t="n"/>
-      <c r="W116" s="10" t="n"/>
-      <c r="X116" s="10" t="n"/>
-      <c r="Y116" s="10" t="n"/>
-      <c r="Z116" s="10" t="n"/>
-      <c r="AA116" s="10" t="n"/>
-      <c r="AB116" s="10" t="n"/>
-      <c r="AC116" s="10" t="n"/>
-      <c r="AD116" s="10" t="n"/>
-      <c r="AE116" s="10" t="n"/>
-      <c r="AF116" s="10" t="n"/>
-      <c r="AG116" s="10" t="n"/>
-      <c r="AH116" s="10" t="n"/>
-      <c r="AI116" s="10" t="n"/>
-      <c r="AJ116" s="10" t="n"/>
-      <c r="AK116" s="11" t="n"/>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="B117" s="27" t="inlineStr">
-        <is>
-          <t>4.7 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="C118" s="41" t="inlineStr">
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="10" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="10" t="n"/>
+      <c r="I124" s="10" t="n"/>
+      <c r="J124" s="10" t="n"/>
+      <c r="K124" s="10" t="n"/>
+      <c r="L124" s="10" t="n"/>
+      <c r="M124" s="10" t="n"/>
+      <c r="N124" s="10" t="n"/>
+      <c r="O124" s="10" t="n"/>
+      <c r="P124" s="10" t="n"/>
+      <c r="Q124" s="10" t="n"/>
+      <c r="R124" s="10" t="n"/>
+      <c r="S124" s="10" t="n"/>
+      <c r="T124" s="10" t="n"/>
+      <c r="U124" s="10" t="n"/>
+      <c r="V124" s="10" t="n"/>
+      <c r="W124" s="10" t="n"/>
+      <c r="X124" s="10" t="n"/>
+      <c r="Y124" s="10" t="n"/>
+      <c r="Z124" s="10" t="n"/>
+      <c r="AA124" s="10" t="n"/>
+      <c r="AB124" s="10" t="n"/>
+      <c r="AC124" s="10" t="n"/>
+      <c r="AD124" s="10" t="n"/>
+      <c r="AE124" s="10" t="n"/>
+      <c r="AF124" s="10" t="n"/>
+      <c r="AG124" s="10" t="n"/>
+      <c r="AH124" s="10" t="n"/>
+      <c r="AI124" s="10" t="n"/>
+      <c r="AJ124" s="10" t="n"/>
+      <c r="AK124" s="11" t="n"/>
+    </row>
+    <row r="125" ht="306" customHeight="1">
+      <c r="C125" s="42" t="inlineStr">
+        <is>
+          <t>before_value：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "kanri_shiten_id": 1,
+  "ja_id": 1,
+  "kanri_shiten_code": "113-3300-001",
+  "kanri_shiten_name": "東京中央会支店",
+  "kanri_shiten_name_kana": "ﾄｳｷｮｳﾁｭｳｵｳｶｲｼﾃﾝ",
+  "todofuken_code": "13",
+  "yubin_no": "1000001",
+  "address": "千代田区千代田1-1-1",
+  "tel": "0312345678",
+  "fax": "0312345679",
+  "paper_flg": true,
+  "denshi_flg": false,
+  "biko": "中央会管轄"
+}</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="n"/>
+      <c r="E125" s="10" t="n"/>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
+      <c r="H125" s="10" t="n"/>
+      <c r="I125" s="10" t="n"/>
+      <c r="J125" s="10" t="n"/>
+      <c r="K125" s="10" t="n"/>
+      <c r="L125" s="10" t="n"/>
+      <c r="M125" s="10" t="n"/>
+      <c r="N125" s="10" t="n"/>
+      <c r="O125" s="10" t="n"/>
+      <c r="P125" s="10" t="n"/>
+      <c r="Q125" s="10" t="n"/>
+      <c r="R125" s="10" t="n"/>
+      <c r="S125" s="10" t="n"/>
+      <c r="T125" s="10" t="n"/>
+      <c r="U125" s="10" t="n"/>
+      <c r="V125" s="10" t="n"/>
+      <c r="W125" s="10" t="n"/>
+      <c r="X125" s="10" t="n"/>
+      <c r="Y125" s="10" t="n"/>
+      <c r="Z125" s="10" t="n"/>
+      <c r="AA125" s="10" t="n"/>
+      <c r="AB125" s="10" t="n"/>
+      <c r="AC125" s="10" t="n"/>
+      <c r="AD125" s="10" t="n"/>
+      <c r="AE125" s="10" t="n"/>
+      <c r="AF125" s="10" t="n"/>
+      <c r="AG125" s="10" t="n"/>
+      <c r="AH125" s="10" t="n"/>
+      <c r="AI125" s="10" t="n"/>
+      <c r="AJ125" s="10" t="n"/>
+      <c r="AK125" s="11" t="n"/>
+    </row>
+    <row r="126" ht="306" customHeight="1">
+      <c r="C126" s="42" t="inlineStr">
+        <is>
+          <t>after_value：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "kanri_shiten_id": 1,
+  "ja_id": 1,
+  "kanri_shiten_code": "113-3300-001",
+  "kanri_shiten_name": "東京中央会支店（改称）",
+  "kanri_shiten_name_kana": "ﾄｳｷｮｳﾁｭｳｵｳｶｲｼﾃﾝ ｶｲｼｮｳ",
+  "todofuken_code": "13",
+  "yubin_no": "1000001",
+  "address": "千代田区千代田1-1-1 改修ビル3F",
+  "tel": "0312345678",
+  "fax": "0312345679",
+  "paper_flg": true,
+  "denshi_flg": true,
+  "biko": "住所変更済み"
+}</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="10" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="10" t="n"/>
+      <c r="I126" s="10" t="n"/>
+      <c r="J126" s="10" t="n"/>
+      <c r="K126" s="10" t="n"/>
+      <c r="L126" s="10" t="n"/>
+      <c r="M126" s="10" t="n"/>
+      <c r="N126" s="10" t="n"/>
+      <c r="O126" s="10" t="n"/>
+      <c r="P126" s="10" t="n"/>
+      <c r="Q126" s="10" t="n"/>
+      <c r="R126" s="10" t="n"/>
+      <c r="S126" s="10" t="n"/>
+      <c r="T126" s="10" t="n"/>
+      <c r="U126" s="10" t="n"/>
+      <c r="V126" s="10" t="n"/>
+      <c r="W126" s="10" t="n"/>
+      <c r="X126" s="10" t="n"/>
+      <c r="Y126" s="10" t="n"/>
+      <c r="Z126" s="10" t="n"/>
+      <c r="AA126" s="10" t="n"/>
+      <c r="AB126" s="10" t="n"/>
+      <c r="AC126" s="10" t="n"/>
+      <c r="AD126" s="10" t="n"/>
+      <c r="AE126" s="10" t="n"/>
+      <c r="AF126" s="10" t="n"/>
+      <c r="AG126" s="10" t="n"/>
+      <c r="AH126" s="10" t="n"/>
+      <c r="AI126" s="10" t="n"/>
+      <c r="AJ126" s="10" t="n"/>
+      <c r="AK126" s="11" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="B127" s="27" t="inlineStr">
+        <is>
+          <t>4.8 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="C128" s="41" t="inlineStr">
         <is>
           <t>更新した管理支店データと成功メッセージを JSON 形式で返却する。</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="C119" s="41" t="inlineStr">
+    <row r="129" ht="18" customHeight="1">
+      <c r="C129" s="41" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="B120" s="27" t="inlineStr">
-        <is>
-          <t>4.8 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="C121" s="41" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="B130" s="27" t="inlineStr">
+        <is>
+          <t>4.9 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="C131" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 Internal Server Error を返却する。</t>
         </is>
       </c>
     </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="C132" s="41" t="inlineStr">
+        <is>
+          <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="288" customHeight="1">
+      <c r="C133" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (
+  log_type, log_datetime, account_id, ja_id,
+  gamen_name, operation, result_status,
+  target_id, target_table,
+  before_value, after_value,
+  error_message, stack_trace,
+  ip_address, user_agent
+)
+VALUES (
+  3, NOW(), :user_account_id, :ja_id,
+  '管理支店マスタ登録画面(ACSMS-SCR-009)', 'UPDATE', 2,
+  :kanri_shiten_id, 'm_kanri_shiten',
+  '', '',
+  :error_message, :stack_trace,
+  :ip_address, :user_agent
+)</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="10" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="10" t="n"/>
+      <c r="J133" s="10" t="n"/>
+      <c r="K133" s="10" t="n"/>
+      <c r="L133" s="10" t="n"/>
+      <c r="M133" s="10" t="n"/>
+      <c r="N133" s="10" t="n"/>
+      <c r="O133" s="10" t="n"/>
+      <c r="P133" s="10" t="n"/>
+      <c r="Q133" s="10" t="n"/>
+      <c r="R133" s="10" t="n"/>
+      <c r="S133" s="10" t="n"/>
+      <c r="T133" s="10" t="n"/>
+      <c r="U133" s="10" t="n"/>
+      <c r="V133" s="10" t="n"/>
+      <c r="W133" s="10" t="n"/>
+      <c r="X133" s="10" t="n"/>
+      <c r="Y133" s="10" t="n"/>
+      <c r="Z133" s="10" t="n"/>
+      <c r="AA133" s="10" t="n"/>
+      <c r="AB133" s="10" t="n"/>
+      <c r="AC133" s="10" t="n"/>
+      <c r="AD133" s="10" t="n"/>
+      <c r="AE133" s="10" t="n"/>
+      <c r="AF133" s="10" t="n"/>
+      <c r="AG133" s="10" t="n"/>
+      <c r="AH133" s="10" t="n"/>
+      <c r="AI133" s="10" t="n"/>
+      <c r="AJ133" s="10" t="n"/>
+      <c r="AK133" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="300">
+  <mergeCells count="322">
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="T53:X53"/>
+    <mergeCell ref="D56:L56"/>
+    <mergeCell ref="C128:AK128"/>
+    <mergeCell ref="T55:X55"/>
+    <mergeCell ref="C113:AK113"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C129:AK129"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="C131:AK131"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="C126:AK126"/>
+    <mergeCell ref="Y53:AE53"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="Y55:AE55"/>
+    <mergeCell ref="C117:AK117"/>
+    <mergeCell ref="A82:AK82"/>
+    <mergeCell ref="T40:X40"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="C115:AK115"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="T45:X45"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="Y33:AB33"/>
+    <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="Y56:AE56"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="D94:AK94"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="T51:X51"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D105:AK105"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="Q54:S54"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="Q57:S57"/>
+    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="Y51:AE51"/>
+    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="D95:AK95"/>
+    <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="M46:P46"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="A37:AK37"/>
+    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="D103:AK103"/>
+    <mergeCell ref="B130:AK130"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B119:AK119"/>
+    <mergeCell ref="D98:AK98"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="B112:AK112"/>
+    <mergeCell ref="B127:AK127"/>
+    <mergeCell ref="C118:AK118"/>
+    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="T46:X46"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="B122:AK122"/>
+    <mergeCell ref="D49:L49"/>
+    <mergeCell ref="T48:X48"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="AF42:AK42"/>
+    <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="D54:L54"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="T56:X56"/>
+    <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="T43:X43"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D57:L57"/>
+    <mergeCell ref="C111:AK111"/>
+    <mergeCell ref="B14:I19"/>
+    <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="M58:P58"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="B83:AK83"/>
+    <mergeCell ref="C124:AK124"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D44:L44"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="C132:AK132"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="D87:AK87"/>
-    <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="T33:X33"/>
-    <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
-    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="B72:I72"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M32:P32"/>
-    <mergeCell ref="C77:AK77"/>
-    <mergeCell ref="N18:AK18"/>
-    <mergeCell ref="M29:P29"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C68:AK68"/>
     <mergeCell ref="Y32:AB32"/>
-    <mergeCell ref="T53:X53"/>
     <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="M46:P46"/>
-    <mergeCell ref="B70:I70"/>
-    <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="M56:P56"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="Y52:AE52"/>
-    <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="C34:L34"/>
-    <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="T55:X55"/>
-    <mergeCell ref="C113:AK113"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="N19:AK19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C100:AK100"/>
-    <mergeCell ref="C112:AK112"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C65:AK65"/>
-    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="C109:AK109"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D51:L51"/>
-    <mergeCell ref="AF52:AK52"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
+    <mergeCell ref="C133:AK133"/>
     <mergeCell ref="Y54:AE54"/>
-    <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="M54:P54"/>
-    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="J2:P3"/>
-    <mergeCell ref="B114:AK114"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="T31:X31"/>
-    <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="C95:AK95"/>
-    <mergeCell ref="D101:AK101"/>
-    <mergeCell ref="Q33:S33"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="C106:AK106"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="A80:AK80"/>
-    <mergeCell ref="A37:AK37"/>
-    <mergeCell ref="M33:P33"/>
-    <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="A21:AK21"/>
-    <mergeCell ref="C39:L39"/>
-    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="T57:X57"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="M47:P47"/>
-    <mergeCell ref="B117:AK117"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D53:L53"/>
-    <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
-    <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
-    <mergeCell ref="C74:AK74"/>
-    <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="D89:AK89"/>
-    <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="Q48:S48"/>
     <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="B78:I78"/>
     <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="C35:L35"/>
-    <mergeCell ref="M51:P51"/>
     <mergeCell ref="D90:AK90"/>
-    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="C59:AK59"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C115:AK115"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="C125:AK125"/>
+    <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="Y57:AE57"/>
+    <mergeCell ref="T42:X42"/>
+    <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="T50:X50"/>
+    <mergeCell ref="T44:X44"/>
+    <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="D96:AK96"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="C120:AK120"/>
+    <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="D91:AK91"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="B107:AK107"/>
+    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="C41:C57"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="Y58:AE58"/>
+    <mergeCell ref="AF46:AK46"/>
+    <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AF48:AK48"/>
+    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="D104:AK104"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="M57:P57"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="N18:AK18"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="N19:AK19"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="C106:AK106"/>
+    <mergeCell ref="M45:P45"/>
+    <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="C101:AK101"/>
+    <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="B116:AK116"/>
+    <mergeCell ref="M44:P44"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="B64:I64"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B81:AK81"/>
-    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="B63:I63"/>
     <mergeCell ref="Q51:S51"/>
-    <mergeCell ref="M27:P27"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
-    <mergeCell ref="D49:L49"/>
     <mergeCell ref="Y27:AB27"/>
-    <mergeCell ref="T48:X48"/>
-    <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="Q50:S50"/>
     <mergeCell ref="T32:X32"/>
-    <mergeCell ref="T45:X45"/>
     <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="Y33:AB33"/>
-    <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="T42:X42"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C62:AK62"/>
-    <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
-    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C82:AK82"/>
-    <mergeCell ref="D92:AK92"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="Q49:S49"/>
-    <mergeCell ref="T50:X50"/>
-    <mergeCell ref="Y56:AE56"/>
-    <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C116:AK116"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="M55:P55"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="D94:AK94"/>
-    <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="D55:L55"/>
-    <mergeCell ref="AF40:AK40"/>
-    <mergeCell ref="M49:P49"/>
     <mergeCell ref="C121:AK121"/>
-    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="M48:P48"/>
-    <mergeCell ref="T51:X51"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="T41:X41"/>
-    <mergeCell ref="C105:AK105"/>
-    <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="AF56:AK56"/>
-    <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="D96:AK96"/>
-    <mergeCell ref="T56:X56"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="AC32:AE32"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="T43:X43"/>
-    <mergeCell ref="C119:AK119"/>
-    <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
-    <mergeCell ref="C56:L56"/>
     <mergeCell ref="V2:Y3"/>
-    <mergeCell ref="N16:AK16"/>
-    <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="Q54:S54"/>
-    <mergeCell ref="Q55:S55"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="D91:AK91"/>
-    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M41:P41"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
-    <mergeCell ref="B14:I19"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q40:S40"/>
     <mergeCell ref="T49:X49"/>
-    <mergeCell ref="B111:AK111"/>
-    <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="D93:AK93"/>
-    <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
-    <mergeCell ref="C41:C55"/>
-    <mergeCell ref="B120:AK120"/>
-    <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B107:AK107"/>
+    <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D85:AK85"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="M52:P52"/>
-    <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="AF46:AK46"/>
-    <mergeCell ref="AF28:AK28"/>
-    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="C58:L58"/>
+    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="Y35:AB35"/>
-    <mergeCell ref="D50:L50"/>
-    <mergeCell ref="D44:L44"/>
-    <mergeCell ref="Q53:S53"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="Y51:AE51"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C71:AK71"/>
-    <mergeCell ref="D86:AK86"/>
-    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="M30:P30"/>
     <mergeCell ref="C110:AK110"/>
-    <mergeCell ref="Q52:S52"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="AF29:AK29"/>
-    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13897,7 +14952,7 @@
       <c r="P2" s="22" t="n"/>
       <c r="Q2" s="20" t="inlineStr">
         <is>
-          <t>ACSMS-API-009-004</t>
+          <t>ACSMS-API-COMMON-001</t>
         </is>
       </c>
       <c r="R2" s="21" t="n"/>
@@ -13922,7 +14977,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/10</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -15007,7 +16062,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="C46" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
